--- a/data/k-props/2026-08-19.xlsx
+++ b/data/k-props/2026-08-19.xlsx
@@ -151,139 +151,139 @@
     <t>&lt;6</t>
   </si>
   <si>
+    <t>Michael King</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ New York Mets</t>
+  </si>
+  <si>
+    <t>Taj Bradley</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Sean Newcomb</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Clay Holmes</t>
+  </si>
+  <si>
+    <t>Brandon Pfaadt</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Payton Tolle</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Aaron Nola</t>
+  </si>
+  <si>
+    <t>Will Warren</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Chris Bassitt</t>
+  </si>
+  <si>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Matthew Liberatore</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Chase Burns</t>
+  </si>
+  <si>
+    <t>Max Scherzer</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Drew Rasmussen</t>
+  </si>
+  <si>
+    <t>Logan Gilbert</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Dustin May</t>
+  </si>
+  <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Kumar Rocker</t>
+  </si>
+  <si>
+    <t>Walbert Ureña</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Roki Sasaki</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Kyle Freeland</t>
+  </si>
+  <si>
     <t>Jackson Jobe</t>
   </si>
   <si>
     <t>Robert Stock</t>
   </si>
   <si>
-    <t>San Diego Padres @ New York Mets</t>
-  </si>
-  <si>
-    <t>Michael King</t>
-  </si>
-  <si>
-    <t>Taj Bradley</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
     <t>AJ Smith-Shawver</t>
   </si>
   <si>
-    <t>Clay Holmes</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Payton Tolle</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Brandon Pfaadt</t>
-  </si>
-  <si>
-    <t>Aaron Nola</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
-  </si>
-  <si>
-    <t>Chris Bassitt</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Will Warren</t>
-  </si>
-  <si>
-    <t>Chase Burns</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Matthew Liberatore</t>
-  </si>
-  <si>
-    <t>Drew Rasmussen</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Max Scherzer</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Parker Messick</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Logan Gilbert</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Dustin May</t>
-  </si>
-  <si>
     <t>Seth Lugo</t>
   </si>
   <si>
     <t>Athletics @ Kansas City Royals</t>
   </si>
   <si>
-    <t>Kumar Rocker</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
-  </si>
-  <si>
     <t>Walbert Urena</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Roki Sasaki</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Kyle Freeland</t>
-  </si>
-  <si>
-    <t>Sean Newcomb</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Walbert Ureña</t>
   </si>
 </sst>
 </file>
@@ -881,7 +881,7 @@
         <v>0.3068</v>
       </c>
       <c r="AG2">
-        <v>0.8321</v>
+        <v>0.832</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -901,28 +901,70 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>104</v>
+        <v>-148</v>
       </c>
       <c r="E3">
-        <v>-117</v>
+        <v>128</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="G3">
+        <v>823587</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I3">
+        <v>5.7</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
       </c>
       <c r="L3">
         <v>6</v>
       </c>
+      <c r="M3">
+        <v>0.212</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>121</v>
+      </c>
+      <c r="P3">
+        <v>4.11</v>
+      </c>
+      <c r="Q3">
+        <v>0.2314</v>
+      </c>
+      <c r="R3">
+        <v>0.377</v>
+      </c>
       <c r="S3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T3">
+        <v>0.236</v>
+      </c>
+      <c r="U3">
+        <v>0.2368</v>
+      </c>
+      <c r="V3">
+        <v>9</v>
+      </c>
+      <c r="W3">
+        <v>0.2253</v>
+      </c>
+      <c r="X3">
+        <v>0.2199</v>
+      </c>
+      <c r="Y3">
+        <v>0.9921</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -930,8 +972,23 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
+      <c r="AD3">
+        <v>5.46</v>
+      </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF3">
+        <v>0.2193</v>
+      </c>
+      <c r="AG3">
+        <v>1.0731</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>5.46</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -939,34 +996,76 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D4">
-        <v>-139</v>
+        <v>-132</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="G4">
+        <v>823664</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I4">
+        <v>5.7</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>0.2608</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>123</v>
+      </c>
+      <c r="P4">
+        <v>4.27</v>
+      </c>
+      <c r="Q4">
+        <v>0.2195</v>
+      </c>
+      <c r="R4">
+        <v>0.381</v>
       </c>
       <c r="S4" t="s">
-        <v>44</v>
-      </c>
-      <c r="V4" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T4">
+        <v>0.2362</v>
+      </c>
+      <c r="U4">
+        <v>0.2336</v>
+      </c>
+      <c r="V4">
+        <v>9</v>
+      </c>
+      <c r="W4">
+        <v>0.2177</v>
+      </c>
+      <c r="X4">
+        <v>0.2199</v>
+      </c>
+      <c r="Y4">
+        <v>1.0473</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -974,8 +1073,23 @@
       <c r="AC4" t="s">
         <v>44</v>
       </c>
+      <c r="AD4">
+        <v>6.65</v>
+      </c>
       <c r="AE4" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="AF4">
+        <v>0.2451</v>
+      </c>
+      <c r="AG4">
+        <v>1.0743</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>6.65</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -983,76 +1097,67 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-      <c r="D5">
-        <v>-148</v>
-      </c>
-      <c r="E5">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G5">
-        <v>823587</v>
+        <v>824640</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.212</v>
+        <v>0.2319</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>121</v>
+        <v>14</v>
       </c>
       <c r="P5">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="Q5">
-        <v>0.2314</v>
+        <v>0.4286</v>
       </c>
       <c r="R5">
-        <v>0.377</v>
+        <v>0.065</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.236</v>
+        <v>0.2115</v>
       </c>
       <c r="U5">
-        <v>0.2368</v>
+        <v>0.2131</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2253</v>
+        <v>0.2191</v>
       </c>
       <c r="X5">
         <v>0.2199</v>
       </c>
       <c r="Y5">
-        <v>0.9921</v>
+        <v>0.8952</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1061,22 +1166,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.46</v>
+        <v>1.85</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2193</v>
+        <v>0.2448</v>
       </c>
       <c r="AG5">
-        <v>1.0733</v>
+        <v>0.9618</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.46</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1084,28 +1189,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D6">
-        <v>-132</v>
+        <v>-125</v>
       </c>
       <c r="E6">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
-        <v>823664</v>
+        <v>824640</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1117,43 +1222,43 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>0.2608</v>
+        <v>0.1922</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="P6">
-        <v>4.27</v>
+        <v>4.03</v>
       </c>
       <c r="Q6">
-        <v>0.2195</v>
+        <v>0.2124</v>
       </c>
       <c r="R6">
-        <v>0.381</v>
+        <v>0.361</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2362</v>
+        <v>0.248</v>
       </c>
       <c r="U6">
-        <v>0.2336</v>
+        <v>0.2503</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2177</v>
+        <v>0.2364</v>
       </c>
       <c r="X6">
         <v>0.2199</v>
       </c>
       <c r="Y6">
-        <v>1.0473</v>
+        <v>1.0504</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1162,22 +1267,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>6.65</v>
+        <v>5.48</v>
       </c>
       <c r="AE6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2451</v>
+        <v>0.1995</v>
       </c>
       <c r="AG6">
-        <v>1.0744</v>
+        <v>1.1277</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>6.65</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1185,34 +1290,76 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D7">
-        <v>132</v>
+        <v>-113</v>
       </c>
       <c r="E7">
-        <v>-165</v>
+        <v>-110</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="G7">
+        <v>824722</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I7">
+        <v>5.9</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
       </c>
       <c r="L7">
         <v>5</v>
       </c>
+      <c r="M7">
+        <v>0.1609</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <v>125</v>
+      </c>
+      <c r="P7">
+        <v>4.09</v>
+      </c>
+      <c r="Q7">
+        <v>0.136</v>
+      </c>
+      <c r="R7">
+        <v>0.385</v>
+      </c>
       <c r="S7" t="s">
-        <v>44</v>
-      </c>
-      <c r="V7" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T7">
+        <v>0.1864</v>
+      </c>
+      <c r="U7">
+        <v>0.1979</v>
+      </c>
+      <c r="V7">
+        <v>9</v>
+      </c>
+      <c r="W7">
+        <v>0.215</v>
+      </c>
+      <c r="X7">
+        <v>0.2199</v>
+      </c>
+      <c r="Y7">
+        <v>1.0088</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1220,8 +1367,23 @@
       <c r="AC7" t="s">
         <v>44</v>
       </c>
+      <c r="AD7">
+        <v>3.15</v>
+      </c>
       <c r="AE7" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF7">
+        <v>0.1514</v>
+      </c>
+      <c r="AG7">
+        <v>0.8478</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>3.15</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1229,22 +1391,22 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D8">
-        <v>-125</v>
+        <v>-115</v>
       </c>
       <c r="E8">
         <v>103</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>824640</v>
+        <v>824722</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
@@ -1262,43 +1424,43 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>0.1922</v>
+        <v>0.2777</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P8">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="Q8">
-        <v>0.2124</v>
+        <v>0.3417</v>
       </c>
       <c r="R8">
-        <v>0.361</v>
+        <v>0.375</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="T8">
-        <v>0.248</v>
+        <v>0.1713</v>
       </c>
       <c r="U8">
-        <v>0.2503</v>
+        <v>0.1717</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2364</v>
+        <v>0.1747</v>
       </c>
       <c r="X8">
         <v>0.2199</v>
       </c>
       <c r="Y8">
-        <v>1.0504</v>
+        <v>0.9162</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1307,22 +1469,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>5.48</v>
+        <v>4.96</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1995</v>
+        <v>0.3017</v>
       </c>
       <c r="AG8">
-        <v>1.1278</v>
+        <v>0.7789</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>5.48</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1330,28 +1492,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D9">
-        <v>-115</v>
+        <v>126</v>
       </c>
       <c r="E9">
-        <v>103</v>
+        <v>-145</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>824722</v>
+        <v>823424</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1363,43 +1525,43 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.2777</v>
+        <v>0.1852</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="P9">
-        <v>4.01</v>
+        <v>4.11</v>
       </c>
       <c r="Q9">
-        <v>0.3417</v>
+        <v>0.1716</v>
       </c>
       <c r="R9">
-        <v>0.375</v>
+        <v>0.401</v>
       </c>
       <c r="S9" t="s">
         <v>58</v>
       </c>
       <c r="T9">
-        <v>0.1713</v>
+        <v>0.1788</v>
       </c>
       <c r="U9">
-        <v>0.1717</v>
+        <v>0.1803</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.1747</v>
+        <v>0.2232</v>
       </c>
       <c r="X9">
         <v>0.2199</v>
       </c>
       <c r="Y9">
-        <v>0.9162</v>
+        <v>0.9683</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1408,22 +1570,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.96</v>
+        <v>3.82</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.3017</v>
+        <v>0.1798</v>
       </c>
       <c r="AG9">
-        <v>0.779</v>
+        <v>0.8132</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.96</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1431,28 +1593,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C10">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D10">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="E10">
-        <v>-110</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>824722</v>
+        <v>823424</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1464,43 +1626,43 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>0.1609</v>
+        <v>0.2434</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="P10">
-        <v>4.09</v>
+        <v>4.36</v>
       </c>
       <c r="Q10">
-        <v>0.136</v>
+        <v>0.2609</v>
       </c>
       <c r="R10">
-        <v>0.385</v>
+        <v>0.365</v>
       </c>
       <c r="S10" t="s">
         <v>58</v>
       </c>
       <c r="T10">
-        <v>0.1946</v>
+        <v>0.2331</v>
       </c>
       <c r="U10">
-        <v>0.1869</v>
+        <v>0.2217</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.215</v>
+        <v>0.2119</v>
       </c>
       <c r="X10">
         <v>0.2199</v>
       </c>
       <c r="Y10">
-        <v>0.9823</v>
+        <v>0.987</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1509,22 +1671,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.2</v>
+        <v>5.93</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1514</v>
+        <v>0.2498</v>
       </c>
       <c r="AG10">
-        <v>0.8851</v>
+        <v>1.0602</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.2</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1532,28 +1694,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11">
         <v>5.5</v>
       </c>
       <c r="D11">
-        <v>-115</v>
+        <v>124</v>
       </c>
       <c r="E11">
-        <v>102</v>
+        <v>-150</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11">
-        <v>823424</v>
+        <v>824801</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1562,46 +1724,46 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2434</v>
+        <v>0.2263</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="P11">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="Q11">
-        <v>0.2609</v>
+        <v>0.2136</v>
       </c>
       <c r="R11">
-        <v>0.365</v>
+        <v>0.34</v>
       </c>
       <c r="S11" t="s">
         <v>58</v>
       </c>
       <c r="T11">
-        <v>0.2331</v>
+        <v>0.2209</v>
       </c>
       <c r="U11">
-        <v>0.2217</v>
+        <v>0.2383</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2119</v>
+        <v>0.2369</v>
       </c>
       <c r="X11">
         <v>0.2199</v>
       </c>
       <c r="Y11">
-        <v>0.987</v>
+        <v>1.0332</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1610,22 +1772,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.93</v>
+        <v>5.15</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.2498</v>
+        <v>0.222</v>
       </c>
       <c r="AG11">
-        <v>1.0603</v>
+        <v>1.0045</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.93</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1633,28 +1795,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <v>4.5</v>
       </c>
       <c r="D12">
-        <v>126</v>
+        <v>-103</v>
       </c>
       <c r="E12">
-        <v>-145</v>
+        <v>-105</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G12">
-        <v>823424</v>
+        <v>824801</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1663,46 +1825,46 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>0.1852</v>
+        <v>0.1404</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="P12">
-        <v>4.11</v>
+        <v>4.62</v>
       </c>
       <c r="Q12">
-        <v>0.1716</v>
+        <v>0.1215</v>
       </c>
       <c r="R12">
-        <v>0.401</v>
+        <v>0.349</v>
       </c>
       <c r="S12" t="s">
         <v>58</v>
       </c>
       <c r="T12">
-        <v>0.1788</v>
+        <v>0.2771</v>
       </c>
       <c r="U12">
-        <v>0.1803</v>
+        <v>0.2738</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2232</v>
+        <v>0.2463</v>
       </c>
       <c r="X12">
         <v>0.2199</v>
       </c>
       <c r="Y12">
-        <v>0.9683</v>
+        <v>1.0317</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1711,22 +1873,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.1798</v>
+        <v>0.1338</v>
       </c>
       <c r="AG12">
-        <v>0.8133</v>
+        <v>1.26</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1734,28 +1896,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C13">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D13">
-        <v>-103</v>
+        <v>125</v>
       </c>
       <c r="E13">
-        <v>-105</v>
+        <v>-130</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G13">
-        <v>824801</v>
+        <v>824394</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1767,43 +1929,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.1404</v>
+        <v>0.2513</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="P13">
-        <v>4.62</v>
+        <v>3.97</v>
       </c>
       <c r="Q13">
-        <v>0.1215</v>
+        <v>0.2667</v>
       </c>
       <c r="R13">
-        <v>0.349</v>
+        <v>0.375</v>
       </c>
       <c r="S13" t="s">
         <v>58</v>
       </c>
       <c r="T13">
-        <v>0.2771</v>
+        <v>0.2077</v>
       </c>
       <c r="U13">
-        <v>0.2738</v>
+        <v>0.2074</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>0.2463</v>
+        <v>0.2287</v>
       </c>
       <c r="X13">
         <v>0.2199</v>
       </c>
       <c r="Y13">
-        <v>1.0317</v>
+        <v>0.9993</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1812,22 +1974,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.75</v>
+        <v>5.71</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.1338</v>
+        <v>0.2571</v>
       </c>
       <c r="AG13">
-        <v>1.2602</v>
+        <v>0.9446</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>3.75</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1835,28 +1997,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>5.5</v>
       </c>
       <c r="D14">
-        <v>124</v>
+        <v>-107</v>
       </c>
       <c r="E14">
-        <v>-150</v>
+        <v>-104</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G14">
-        <v>824801</v>
+        <v>824476</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1868,43 +2030,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.2263</v>
+        <v>0.2235</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="P14">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="Q14">
-        <v>0.2136</v>
+        <v>0.2617</v>
       </c>
       <c r="R14">
-        <v>0.34</v>
+        <v>0.349</v>
       </c>
       <c r="S14" t="s">
         <v>58</v>
       </c>
       <c r="T14">
-        <v>0.2209</v>
+        <v>0.2676</v>
       </c>
       <c r="U14">
-        <v>0.2383</v>
+        <v>0.2718</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2369</v>
+        <v>0.2505</v>
       </c>
       <c r="X14">
         <v>0.2199</v>
       </c>
       <c r="Y14">
-        <v>1.0332</v>
+        <v>1.0326</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1913,22 +2075,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.15</v>
+        <v>6.43</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF14">
-        <v>0.222</v>
+        <v>0.2368</v>
       </c>
       <c r="AG14">
-        <v>1.0047</v>
+        <v>1.2168</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>5.15</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1936,7 +2098,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C15">
         <v>6.5</v>
@@ -1948,7 +2110,7 @@
         <v>-130</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>824476</v>
@@ -2014,7 +2176,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.59</v>
+        <v>5.58</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2023,13 +2185,13 @@
         <v>0.2889</v>
       </c>
       <c r="AG15">
-        <v>0.8967</v>
+        <v>0.8966</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.59</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2037,28 +2199,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C16">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D16">
+        <v>-113</v>
+      </c>
+      <c r="E16">
         <v>-107</v>
       </c>
-      <c r="E16">
-        <v>-104</v>
-      </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G16">
-        <v>824476</v>
+        <v>822937</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2070,43 +2232,43 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>0.2235</v>
+        <v>0.1713</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="P16">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="Q16">
-        <v>0.2617</v>
+        <v>0.2165</v>
       </c>
       <c r="R16">
-        <v>0.349</v>
+        <v>0.327</v>
       </c>
       <c r="S16" t="s">
         <v>58</v>
       </c>
       <c r="T16">
-        <v>0.2676</v>
+        <v>0.1771</v>
       </c>
       <c r="U16">
-        <v>0.2718</v>
+        <v>0.1754</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2505</v>
+        <v>0.1884</v>
       </c>
       <c r="X16">
         <v>0.2199</v>
       </c>
       <c r="Y16">
-        <v>1.0326</v>
+        <v>0.9042</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2115,22 +2277,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>6.44</v>
+        <v>2.45</v>
       </c>
       <c r="AE16" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.2368</v>
+        <v>0.186</v>
       </c>
       <c r="AG16">
-        <v>1.217</v>
+        <v>0.8056</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>6.44</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2138,7 +2300,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C17">
         <v>5.5</v>
@@ -2150,7 +2312,7 @@
         <v>-155</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17">
         <v>822937</v>
@@ -2225,7 +2387,7 @@
         <v>0.2789</v>
       </c>
       <c r="AG17">
-        <v>0.8807</v>
+        <v>0.8806</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -2239,28 +2401,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C18">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D18">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="E18">
-        <v>-107</v>
+        <v>-115</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G18">
-        <v>822937</v>
+        <v>823748</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I18">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2272,43 +2434,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.1713</v>
+        <v>0.2662</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="P18">
-        <v>4.41</v>
+        <v>3.93</v>
       </c>
       <c r="Q18">
-        <v>0.2165</v>
+        <v>0.2705</v>
       </c>
       <c r="R18">
-        <v>0.327</v>
+        <v>0.379</v>
       </c>
       <c r="S18" t="s">
         <v>58</v>
       </c>
       <c r="T18">
-        <v>0.1771</v>
+        <v>0.2278</v>
       </c>
       <c r="U18">
-        <v>0.1754</v>
+        <v>0.2279</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>0.1884</v>
+        <v>0.2141</v>
       </c>
       <c r="X18">
         <v>0.2199</v>
       </c>
       <c r="Y18">
-        <v>0.9042</v>
+        <v>1.0015</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2317,22 +2479,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>2.45</v>
+        <v>6.61</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF18">
-        <v>0.186</v>
+        <v>0.2678</v>
       </c>
       <c r="AG18">
-        <v>0.8057</v>
+        <v>1.036</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>2.45</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2340,28 +2502,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C19">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D19">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E19">
-        <v>-130</v>
+        <v>-125</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G19">
-        <v>824394</v>
+        <v>823748</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2373,43 +2535,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2513</v>
+        <v>0.2308</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P19">
-        <v>3.97</v>
+        <v>4.16</v>
       </c>
       <c r="Q19">
-        <v>0.2667</v>
+        <v>0.2373</v>
       </c>
       <c r="R19">
-        <v>0.375</v>
+        <v>0.371</v>
       </c>
       <c r="S19" t="s">
         <v>58</v>
       </c>
       <c r="T19">
-        <v>0.2077</v>
+        <v>0.2159</v>
       </c>
       <c r="U19">
-        <v>0.2074</v>
+        <v>0.2005</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2287</v>
+        <v>0.2245</v>
       </c>
       <c r="X19">
         <v>0.2199</v>
       </c>
       <c r="Y19">
-        <v>0.9993</v>
+        <v>0.9945</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2418,22 +2580,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.71</v>
+        <v>5.02</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2571</v>
+        <v>0.2332</v>
       </c>
       <c r="AG19">
-        <v>0.9447</v>
+        <v>0.9817</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.71</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2441,28 +2603,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C20">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D20">
-        <v>-108</v>
+        <v>-120</v>
       </c>
       <c r="E20">
-        <v>-115</v>
+        <v>110</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G20">
-        <v>823748</v>
+        <v>822860</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2474,43 +2636,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2662</v>
+        <v>0.2612</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P20">
-        <v>3.93</v>
+        <v>4.23</v>
       </c>
       <c r="Q20">
-        <v>0.2705</v>
+        <v>0.2581</v>
       </c>
       <c r="R20">
-        <v>0.379</v>
+        <v>0.383</v>
       </c>
       <c r="S20" t="s">
         <v>58</v>
       </c>
       <c r="T20">
-        <v>0.2278</v>
+        <v>0.2166</v>
       </c>
       <c r="U20">
-        <v>0.2279</v>
+        <v>0.2336</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2141</v>
+        <v>0.222</v>
       </c>
       <c r="X20">
         <v>0.2199</v>
       </c>
       <c r="Y20">
-        <v>1.0015</v>
+        <v>1.0062</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2519,22 +2681,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>6.61</v>
+        <v>5.73</v>
       </c>
       <c r="AE20" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.2678</v>
+        <v>0.26</v>
       </c>
       <c r="AG20">
-        <v>1.0362</v>
+        <v>0.9852</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>6.61</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2542,28 +2704,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C21">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D21">
-        <v>110</v>
+        <v>-125</v>
       </c>
       <c r="E21">
-        <v>-125</v>
+        <v>116</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G21">
-        <v>823748</v>
+        <v>822860</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2575,43 +2737,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2308</v>
+        <v>0.2095</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P21">
-        <v>4.16</v>
+        <v>4.36</v>
       </c>
       <c r="Q21">
-        <v>0.2373</v>
+        <v>0.2241</v>
       </c>
       <c r="R21">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="S21" t="s">
         <v>58</v>
       </c>
       <c r="T21">
-        <v>0.2159</v>
+        <v>0.2087</v>
       </c>
       <c r="U21">
-        <v>0.2005</v>
+        <v>0.2149</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2245</v>
+        <v>0.2078</v>
       </c>
       <c r="X21">
         <v>0.2199</v>
       </c>
       <c r="Y21">
-        <v>0.9945</v>
+        <v>1.0169</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2620,22 +2782,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.02</v>
+        <v>4.45</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2332</v>
+        <v>0.2149</v>
       </c>
       <c r="AG21">
-        <v>0.9819</v>
+        <v>0.9493</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.02</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2643,34 +2805,67 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22">
-        <v>4.5</v>
-      </c>
-      <c r="D22">
-        <v>128</v>
-      </c>
-      <c r="E22">
-        <v>-122</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" t="s">
-        <v>44</v>
+        <v>81</v>
+      </c>
+      <c r="G22">
+        <v>824155</v>
       </c>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I22">
+        <v>5.3</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0.2222</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22">
+        <v>105</v>
+      </c>
+      <c r="P22">
+        <v>4.26</v>
+      </c>
+      <c r="Q22">
+        <v>0.2286</v>
+      </c>
+      <c r="R22">
+        <v>0.344</v>
       </c>
       <c r="S22" t="s">
-        <v>44</v>
-      </c>
-      <c r="V22" t="s">
-        <v>44</v>
+        <v>58</v>
+      </c>
+      <c r="T22">
+        <v>0.2069</v>
+      </c>
+      <c r="U22">
+        <v>0.1979</v>
+      </c>
+      <c r="V22">
+        <v>8</v>
+      </c>
+      <c r="W22">
+        <v>0.2173</v>
+      </c>
+      <c r="X22">
+        <v>0.2199</v>
+      </c>
+      <c r="Y22">
+        <v>0.9851</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2678,8 +2873,23 @@
       <c r="AC22" t="s">
         <v>44</v>
       </c>
+      <c r="AD22">
+        <v>4.7</v>
+      </c>
       <c r="AE22" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF22">
+        <v>0.2244</v>
+      </c>
+      <c r="AG22">
+        <v>0.9407</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>4.7</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2687,28 +2897,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C23">
         <v>4.5</v>
       </c>
       <c r="D23">
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="E23">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G23">
-        <v>822860</v>
+        <v>824318</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2717,46 +2927,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>0.2095</v>
+        <v>0.2293</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="P23">
-        <v>4.36</v>
+        <v>4.24</v>
       </c>
       <c r="Q23">
-        <v>0.2241</v>
+        <v>0.2353</v>
       </c>
       <c r="R23">
-        <v>0.367</v>
+        <v>0.373</v>
       </c>
       <c r="S23" t="s">
         <v>58</v>
       </c>
       <c r="T23">
-        <v>0.2087</v>
+        <v>0.2228</v>
       </c>
       <c r="U23">
-        <v>0.2149</v>
+        <v>0.2203</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2078</v>
+        <v>0.2167</v>
       </c>
       <c r="X23">
         <v>0.2199</v>
       </c>
       <c r="Y23">
-        <v>1.0169</v>
+        <v>1.0193</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2765,22 +2975,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.45</v>
+        <v>5.36</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2149</v>
+        <v>0.2315</v>
       </c>
       <c r="AG23">
-        <v>0.9494</v>
+        <v>1.0132</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.45</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2788,28 +2998,28 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C24">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D24">
-        <v>-120</v>
+        <v>-130</v>
       </c>
       <c r="E24">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G24">
-        <v>822860</v>
+        <v>824318</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2818,46 +3028,46 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>0.2612</v>
+        <v>0.1828</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="P24">
-        <v>4.23</v>
+        <v>4.44</v>
       </c>
       <c r="Q24">
-        <v>0.2581</v>
+        <v>0.1418</v>
       </c>
       <c r="R24">
-        <v>0.383</v>
+        <v>0.401</v>
       </c>
       <c r="S24" t="s">
         <v>58</v>
       </c>
       <c r="T24">
-        <v>0.2166</v>
+        <v>0.2756</v>
       </c>
       <c r="U24">
-        <v>0.2336</v>
+        <v>0.21</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.222</v>
+        <v>0.2007</v>
       </c>
       <c r="X24">
         <v>0.2199</v>
       </c>
       <c r="Y24">
-        <v>1.0062</v>
+        <v>0.9927</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2866,22 +3076,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.73</v>
+        <v>5.04</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.26</v>
+        <v>0.1664</v>
       </c>
       <c r="AG24">
-        <v>0.9853</v>
+        <v>1.2534</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>5.73</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2889,19 +3099,19 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C25">
         <v>4.5</v>
       </c>
       <c r="D25">
-        <v>-114</v>
+        <v>104</v>
       </c>
       <c r="E25">
-        <v>105</v>
+        <v>-117</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="G25" t="s">
         <v>44</v>
@@ -2933,76 +3143,34 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D26">
-        <v>-142</v>
+        <v>-139</v>
       </c>
       <c r="E26">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
-      </c>
-      <c r="G26">
-        <v>824318</v>
+        <v>47</v>
+      </c>
+      <c r="G26" t="s">
+        <v>44</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
-      </c>
-      <c r="I26">
-        <v>5.3</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L26">
-        <v>5</v>
-      </c>
-      <c r="M26">
-        <v>0.2293</v>
-      </c>
-      <c r="N26">
-        <v>5</v>
-      </c>
-      <c r="O26">
-        <v>119</v>
-      </c>
-      <c r="P26">
-        <v>4.24</v>
-      </c>
-      <c r="Q26">
-        <v>0.2353</v>
-      </c>
-      <c r="R26">
-        <v>0.373</v>
+        <v>6</v>
       </c>
       <c r="S26" t="s">
-        <v>58</v>
-      </c>
-      <c r="T26">
-        <v>0.2228</v>
-      </c>
-      <c r="U26">
-        <v>0.2203</v>
-      </c>
-      <c r="V26">
-        <v>9</v>
-      </c>
-      <c r="W26">
-        <v>0.2167</v>
-      </c>
-      <c r="X26">
-        <v>0.2199</v>
-      </c>
-      <c r="Y26">
-        <v>1.0193</v>
+        <v>44</v>
+      </c>
+      <c r="V26" t="s">
+        <v>44</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3010,23 +3178,8 @@
       <c r="AC26" t="s">
         <v>44</v>
       </c>
-      <c r="AD26">
-        <v>5.36</v>
-      </c>
       <c r="AE26" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF26">
-        <v>0.2315</v>
-      </c>
-      <c r="AG26">
-        <v>1.0134</v>
-      </c>
-      <c r="AH26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>5.36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3037,73 +3190,31 @@
         <v>87</v>
       </c>
       <c r="C27">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D27">
-        <v>-130</v>
+        <v>132</v>
       </c>
       <c r="E27">
-        <v>115</v>
+        <v>-165</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
-      </c>
-      <c r="G27">
-        <v>824318</v>
+        <v>49</v>
+      </c>
+      <c r="G27" t="s">
+        <v>44</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
-      </c>
-      <c r="I27">
-        <v>5.5</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L27">
         <v>5</v>
       </c>
-      <c r="M27">
-        <v>0.1828</v>
-      </c>
-      <c r="N27">
-        <v>5</v>
-      </c>
-      <c r="O27">
-        <v>134</v>
-      </c>
-      <c r="P27">
-        <v>4.44</v>
-      </c>
-      <c r="Q27">
-        <v>0.1418</v>
-      </c>
-      <c r="R27">
-        <v>0.401</v>
-      </c>
       <c r="S27" t="s">
-        <v>58</v>
-      </c>
-      <c r="T27">
-        <v>0.2756</v>
-      </c>
-      <c r="U27">
-        <v>0.21</v>
-      </c>
-      <c r="V27">
-        <v>9</v>
-      </c>
-      <c r="W27">
-        <v>0.2007</v>
-      </c>
-      <c r="X27">
-        <v>0.2199</v>
-      </c>
-      <c r="Y27">
-        <v>0.9927</v>
+        <v>44</v>
+      </c>
+      <c r="V27" t="s">
+        <v>44</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3111,23 +3222,8 @@
       <c r="AC27" t="s">
         <v>44</v>
       </c>
-      <c r="AD27">
-        <v>5.04</v>
-      </c>
       <c r="AE27" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF27">
-        <v>0.1664</v>
-      </c>
-      <c r="AG27">
-        <v>1.2536</v>
-      </c>
-      <c r="AH27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>5.04</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3137,65 +3233,32 @@
       <c r="B28" t="s">
         <v>88</v>
       </c>
+      <c r="C28">
+        <v>4.5</v>
+      </c>
+      <c r="D28">
+        <v>128</v>
+      </c>
+      <c r="E28">
+        <v>-122</v>
+      </c>
       <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28">
-        <v>824640</v>
+        <v>89</v>
+      </c>
+      <c r="G28" t="s">
+        <v>44</v>
       </c>
       <c r="H28" t="s">
-        <v>89</v>
-      </c>
-      <c r="I28">
-        <v>2.2</v>
-      </c>
-      <c r="J28" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0.2319</v>
-      </c>
-      <c r="N28">
-        <v>2</v>
-      </c>
-      <c r="O28">
-        <v>14</v>
-      </c>
-      <c r="P28">
-        <v>4.06</v>
-      </c>
-      <c r="Q28">
-        <v>0.4286</v>
-      </c>
-      <c r="R28">
-        <v>0.065</v>
+        <v>6</v>
       </c>
       <c r="S28" t="s">
-        <v>58</v>
-      </c>
-      <c r="T28">
-        <v>0.2192</v>
-      </c>
-      <c r="U28">
-        <v>0.2173</v>
-      </c>
-      <c r="V28">
-        <v>9</v>
-      </c>
-      <c r="W28">
-        <v>0.2191</v>
-      </c>
-      <c r="X28">
-        <v>0.2199</v>
-      </c>
-      <c r="Y28">
-        <v>0.9612</v>
+        <v>44</v>
+      </c>
+      <c r="V28" t="s">
+        <v>44</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3203,23 +3266,8 @@
       <c r="AC28" t="s">
         <v>44</v>
       </c>
-      <c r="AD28">
-        <v>2.06</v>
-      </c>
       <c r="AE28" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF28">
-        <v>0.2448</v>
-      </c>
-      <c r="AG28">
-        <v>0.997</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>2.06</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3229,65 +3277,32 @@
       <c r="B29" t="s">
         <v>90</v>
       </c>
+      <c r="C29">
+        <v>4.5</v>
+      </c>
+      <c r="D29">
+        <v>-114</v>
+      </c>
+      <c r="E29">
+        <v>105</v>
+      </c>
       <c r="F29" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29">
-        <v>824155</v>
+        <v>81</v>
+      </c>
+      <c r="G29" t="s">
+        <v>44</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
-      </c>
-      <c r="I29">
-        <v>5.3</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0.2222</v>
-      </c>
-      <c r="N29">
-        <v>5</v>
-      </c>
-      <c r="O29">
-        <v>105</v>
-      </c>
-      <c r="P29">
-        <v>4.26</v>
-      </c>
-      <c r="Q29">
-        <v>0.2286</v>
-      </c>
-      <c r="R29">
-        <v>0.344</v>
+        <v>6</v>
       </c>
       <c r="S29" t="s">
-        <v>58</v>
-      </c>
-      <c r="T29">
-        <v>0.2069</v>
-      </c>
-      <c r="U29">
-        <v>0.1979</v>
-      </c>
-      <c r="V29">
-        <v>8</v>
-      </c>
-      <c r="W29">
-        <v>0.2173</v>
-      </c>
-      <c r="X29">
-        <v>0.2199</v>
-      </c>
-      <c r="Y29">
-        <v>0.9851</v>
+        <v>44</v>
+      </c>
+      <c r="V29" t="s">
+        <v>44</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3295,23 +3310,8 @@
       <c r="AC29" t="s">
         <v>44</v>
       </c>
-      <c r="AD29">
-        <v>4.7</v>
-      </c>
       <c r="AE29" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF29">
-        <v>0.2244</v>
-      </c>
-      <c r="AG29">
-        <v>0.9409</v>
-      </c>
-      <c r="AH29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>4.7</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-19.xlsx
+++ b/data/k-props/2026-08-19.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>date</t>
   </si>
@@ -133,157 +133,160 @@
     <t>08/19/2026</t>
   </si>
   <si>
+    <t>Michael King</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ New York Mets</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>AJ Smith-Shawver</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Clay Holmes</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Payton Tolle</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Brandon Pfaadt</t>
+  </si>
+  <si>
+    <t>Aaron Nola</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Chris Bassitt</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Will Warren</t>
+  </si>
+  <si>
+    <t>Chase Burns</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Matthew Liberatore</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Drew Rasmussen</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Max Scherzer</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Logan Gilbert</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Dustin May</t>
+  </si>
+  <si>
+    <t>Seth Lugo</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Kumar Rocker</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Walbert Urena</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Roki Sasaki</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Kyle Freeland</t>
+  </si>
+  <si>
     <t>Paul Skenes</t>
   </si>
   <si>
     <t>Detroit Tigers @ Pittsburgh Pirates</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Michael King</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ New York Mets</t>
+    <t>Robert Stock</t>
   </si>
   <si>
     <t>Taj Bradley</t>
   </si>
   <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
     <t>Sean Newcomb</t>
   </si>
   <si>
-    <t>Chicago White Sox @ Chicago Cubs</t>
-  </si>
-  <si>
     <t>Opener / bullpen game</t>
   </si>
   <si>
-    <t>Clay Holmes</t>
-  </si>
-  <si>
-    <t>Brandon Pfaadt</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Payton Tolle</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>Aaron Nola</t>
-  </si>
-  <si>
-    <t>Will Warren</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Chris Bassitt</t>
-  </si>
-  <si>
-    <t>Parker Messick</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Matthew Liberatore</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Chase Burns</t>
-  </si>
-  <si>
-    <t>Max Scherzer</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Drew Rasmussen</t>
-  </si>
-  <si>
-    <t>Logan Gilbert</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Dustin May</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Kumar Rocker</t>
-  </si>
-  <si>
     <t>Walbert Ureña</t>
   </si>
   <si>
-    <t>Los Angeles Angels @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Roki Sasaki</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Kyle Freeland</t>
-  </si>
-  <si>
     <t>Jackson Jobe</t>
-  </si>
-  <si>
-    <t>Robert Stock</t>
-  </si>
-  <si>
-    <t>AJ Smith-Shawver</t>
-  </si>
-  <si>
-    <t>Seth Lugo</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Walbert Urena</t>
   </si>
 </sst>
 </file>
@@ -797,25 +800,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E2">
-        <v>-162</v>
+        <v>-165</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823342</v>
+        <v>823587</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -824,46 +827,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>0.3002</v>
+        <v>0.2112</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P2">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="Q2">
-        <v>0.3186</v>
+        <v>0.2193</v>
       </c>
       <c r="R2">
-        <v>0.361</v>
+        <v>0.363</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.183</v>
+        <v>0.236</v>
       </c>
       <c r="U2">
-        <v>0.1827</v>
+        <v>0.2368</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2228</v>
+        <v>0.2253</v>
       </c>
       <c r="X2">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y2">
-        <v>0.9157</v>
+        <v>0.9921</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -872,22 +875,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>5.17</v>
+        <v>5.28</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.3068</v>
+        <v>0.2142</v>
       </c>
       <c r="AG2">
-        <v>0.832</v>
+        <v>1.0658</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>5.17</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -898,73 +901,31 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-148</v>
+        <v>-245</v>
       </c>
       <c r="E3">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="F3" t="s">
         <v>47</v>
       </c>
-      <c r="G3">
-        <v>823587</v>
+      <c r="G3" t="s">
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3">
-        <v>5.7</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>0.212</v>
-      </c>
-      <c r="N3">
-        <v>5</v>
-      </c>
-      <c r="O3">
-        <v>121</v>
-      </c>
-      <c r="P3">
-        <v>4.11</v>
-      </c>
-      <c r="Q3">
-        <v>0.2314</v>
-      </c>
-      <c r="R3">
-        <v>0.377</v>
+        <v>1</v>
       </c>
       <c r="S3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3">
-        <v>0.236</v>
-      </c>
-      <c r="U3">
-        <v>0.2368</v>
-      </c>
-      <c r="V3">
-        <v>9</v>
-      </c>
-      <c r="W3">
-        <v>0.2253</v>
-      </c>
-      <c r="X3">
-        <v>0.2199</v>
-      </c>
-      <c r="Y3">
-        <v>0.9921</v>
+        <v>44</v>
+      </c>
+      <c r="V3" t="s">
+        <v>44</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -972,23 +933,8 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
-      <c r="AD3">
-        <v>5.46</v>
-      </c>
       <c r="AE3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF3">
-        <v>0.2193</v>
-      </c>
-      <c r="AG3">
-        <v>1.0731</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>5.46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -999,25 +945,25 @@
         <v>48</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-132</v>
+        <v>125</v>
       </c>
       <c r="E4">
-        <v>108</v>
+        <v>-170</v>
       </c>
       <c r="F4" t="s">
         <v>49</v>
       </c>
       <c r="G4">
-        <v>823664</v>
+        <v>824640</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1026,46 +972,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>0.2608</v>
+        <v>0.1842</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="P4">
-        <v>4.27</v>
+        <v>4.03</v>
       </c>
       <c r="Q4">
-        <v>0.2195</v>
+        <v>0.1895</v>
       </c>
       <c r="R4">
-        <v>0.381</v>
+        <v>0.322</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2362</v>
+        <v>0.248</v>
       </c>
       <c r="U4">
-        <v>0.2336</v>
+        <v>0.2503</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2177</v>
+        <v>0.2364</v>
       </c>
       <c r="X4">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y4">
-        <v>1.0473</v>
+        <v>1.0504</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1074,22 +1020,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>6.65</v>
+        <v>4.85</v>
       </c>
       <c r="AE4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2451</v>
+        <v>0.1859</v>
       </c>
       <c r="AG4">
-        <v>1.0743</v>
+        <v>1.1199</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>6.65</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1097,67 +1043,76 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+      <c r="D5">
+        <v>-120</v>
+      </c>
+      <c r="E5">
+        <v>102</v>
+      </c>
+      <c r="F5" t="s">
         <v>51</v>
       </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
       <c r="G5">
-        <v>824640</v>
+        <v>824722</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I5">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>0.2319</v>
+        <v>0.2777</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="P5">
-        <v>4.06</v>
+        <v>4.01</v>
       </c>
       <c r="Q5">
-        <v>0.4286</v>
+        <v>0.3417</v>
       </c>
       <c r="R5">
-        <v>0.065</v>
+        <v>0.375</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2115</v>
+        <v>0.2328</v>
       </c>
       <c r="U5">
-        <v>0.2131</v>
+        <v>0.1756</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2191</v>
+        <v>0.1747</v>
       </c>
       <c r="X5">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y5">
-        <v>0.8952</v>
+        <v>0.88</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1166,22 +1121,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>1.85</v>
+        <v>6.43</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF5">
-        <v>0.2448</v>
+        <v>0.3017</v>
       </c>
       <c r="AG5">
-        <v>0.9618</v>
+        <v>1.0514</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.85</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1189,28 +1144,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D6">
-        <v>-125</v>
+        <v>-114</v>
       </c>
       <c r="E6">
-        <v>103</v>
+        <v>-104</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>824640</v>
+        <v>824722</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1222,43 +1177,43 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>0.1922</v>
+        <v>0.1609</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="P6">
-        <v>4.03</v>
+        <v>4.09</v>
       </c>
       <c r="Q6">
-        <v>0.2124</v>
+        <v>0.136</v>
       </c>
       <c r="R6">
-        <v>0.361</v>
+        <v>0.385</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.248</v>
+        <v>0.1864</v>
       </c>
       <c r="U6">
-        <v>0.2503</v>
+        <v>0.1979</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2364</v>
+        <v>0.215</v>
       </c>
       <c r="X6">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y6">
-        <v>1.0504</v>
+        <v>1.0088</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1267,22 +1222,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>5.48</v>
+        <v>3.13</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.1995</v>
+        <v>0.1514</v>
       </c>
       <c r="AG6">
-        <v>1.1277</v>
+        <v>0.8419</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>5.48</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1290,28 +1245,28 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+      <c r="D7">
+        <v>-124</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s">
         <v>55</v>
       </c>
-      <c r="C7">
-        <v>3.5</v>
-      </c>
-      <c r="D7">
-        <v>-113</v>
-      </c>
-      <c r="E7">
-        <v>-110</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
       <c r="G7">
-        <v>824722</v>
+        <v>823424</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
       <c r="I7">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1323,43 +1278,43 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>0.1609</v>
+        <v>0.2434</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="P7">
-        <v>4.09</v>
+        <v>4.36</v>
       </c>
       <c r="Q7">
-        <v>0.136</v>
+        <v>0.2609</v>
       </c>
       <c r="R7">
-        <v>0.385</v>
+        <v>0.365</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="T7">
-        <v>0.1864</v>
+        <v>0.2331</v>
       </c>
       <c r="U7">
-        <v>0.1979</v>
+        <v>0.2217</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.215</v>
+        <v>0.2119</v>
       </c>
       <c r="X7">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y7">
-        <v>1.0088</v>
+        <v>0.987</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1368,22 +1323,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.15</v>
+        <v>5.89</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.1514</v>
+        <v>0.2498</v>
       </c>
       <c r="AG7">
-        <v>0.8478</v>
+        <v>1.0529</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>3.15</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1394,25 +1349,25 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D8">
-        <v>-115</v>
+        <v>126</v>
       </c>
       <c r="E8">
-        <v>103</v>
+        <v>-145</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>824722</v>
+        <v>823424</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1424,43 +1379,43 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>0.2777</v>
+        <v>0.1852</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="P8">
-        <v>4.01</v>
+        <v>4.11</v>
       </c>
       <c r="Q8">
-        <v>0.3417</v>
+        <v>0.1716</v>
       </c>
       <c r="R8">
-        <v>0.375</v>
+        <v>0.401</v>
       </c>
       <c r="S8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.1713</v>
+        <v>0.1831</v>
       </c>
       <c r="U8">
-        <v>0.1717</v>
+        <v>0.1751</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.1747</v>
+        <v>0.2232</v>
       </c>
       <c r="X8">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y8">
-        <v>0.9162</v>
+        <v>0.9247</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1469,22 +1424,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.96</v>
+        <v>3.71</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.3017</v>
+        <v>0.1798</v>
       </c>
       <c r="AG8">
-        <v>0.7789</v>
+        <v>0.8269</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.96</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1492,28 +1447,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>4.5</v>
       </c>
       <c r="D9">
-        <v>126</v>
+        <v>-113</v>
       </c>
       <c r="E9">
-        <v>-145</v>
+        <v>-110</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
-        <v>823424</v>
+        <v>824801</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1525,43 +1480,43 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.1852</v>
+        <v>0.1404</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="P9">
-        <v>4.11</v>
+        <v>4.62</v>
       </c>
       <c r="Q9">
-        <v>0.1716</v>
+        <v>0.1215</v>
       </c>
       <c r="R9">
-        <v>0.401</v>
+        <v>0.349</v>
       </c>
       <c r="S9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T9">
-        <v>0.1788</v>
+        <v>0.2771</v>
       </c>
       <c r="U9">
-        <v>0.1803</v>
+        <v>0.2738</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2232</v>
+        <v>0.2463</v>
       </c>
       <c r="X9">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y9">
-        <v>0.9683</v>
+        <v>1.0317</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1570,22 +1525,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.1798</v>
+        <v>0.1338</v>
       </c>
       <c r="AG9">
-        <v>0.8132</v>
+        <v>1.2514</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1593,28 +1548,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>5.5</v>
       </c>
       <c r="D10">
-        <v>-115</v>
+        <v>122</v>
       </c>
       <c r="E10">
-        <v>102</v>
+        <v>-150</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
-        <v>823424</v>
+        <v>824801</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1623,46 +1578,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2434</v>
+        <v>0.2263</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="P10">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="Q10">
-        <v>0.2609</v>
+        <v>0.2136</v>
       </c>
       <c r="R10">
-        <v>0.365</v>
+        <v>0.34</v>
       </c>
       <c r="S10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T10">
-        <v>0.2331</v>
+        <v>0.2209</v>
       </c>
       <c r="U10">
-        <v>0.2217</v>
+        <v>0.2383</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2119</v>
+        <v>0.2369</v>
       </c>
       <c r="X10">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y10">
-        <v>0.987</v>
+        <v>1.0332</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1671,22 +1626,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>5.93</v>
+        <v>5.11</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2498</v>
+        <v>0.222</v>
       </c>
       <c r="AG10">
-        <v>1.0602</v>
+        <v>0.9976</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>5.93</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1694,28 +1649,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+      <c r="D11">
+        <v>115</v>
+      </c>
+      <c r="E11">
+        <v>-124</v>
+      </c>
+      <c r="F11" t="s">
         <v>62</v>
       </c>
-      <c r="C11">
-        <v>5.5</v>
-      </c>
-      <c r="D11">
-        <v>124</v>
-      </c>
-      <c r="E11">
-        <v>-150</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
       <c r="G11">
-        <v>824801</v>
+        <v>824476</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1727,43 +1682,43 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2263</v>
+        <v>0.2871</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="P11">
-        <v>4.38</v>
+        <v>4.02</v>
       </c>
       <c r="Q11">
-        <v>0.2136</v>
+        <v>0.292</v>
       </c>
       <c r="R11">
-        <v>0.34</v>
+        <v>0.361</v>
       </c>
       <c r="S11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T11">
-        <v>0.2209</v>
+        <v>0.1971</v>
       </c>
       <c r="U11">
-        <v>0.2383</v>
+        <v>0.1959</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>0.2369</v>
+        <v>0.2131</v>
       </c>
       <c r="X11">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y11">
-        <v>1.0332</v>
+        <v>0.9429</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1772,22 +1727,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.15</v>
+        <v>5.55</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.222</v>
+        <v>0.2889</v>
       </c>
       <c r="AG11">
-        <v>1.0045</v>
+        <v>0.8904</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.15</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1795,28 +1750,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D12">
-        <v>-103</v>
+        <v>-115</v>
       </c>
       <c r="E12">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12">
-        <v>824801</v>
+        <v>824476</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1828,7 +1783,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.1404</v>
+        <v>0.2235</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1837,34 +1792,34 @@
         <v>107</v>
       </c>
       <c r="P12">
-        <v>4.62</v>
+        <v>4.36</v>
       </c>
       <c r="Q12">
-        <v>0.1215</v>
+        <v>0.2617</v>
       </c>
       <c r="R12">
         <v>0.349</v>
       </c>
       <c r="S12" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2771</v>
+        <v>0.2942</v>
       </c>
       <c r="U12">
-        <v>0.2738</v>
+        <v>0.2795</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2463</v>
+        <v>0.2505</v>
       </c>
       <c r="X12">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y12">
-        <v>1.0317</v>
+        <v>1.0673</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1873,22 +1828,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.75</v>
+        <v>7.26</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="AF12">
-        <v>0.1338</v>
+        <v>0.2368</v>
       </c>
       <c r="AG12">
-        <v>1.26</v>
+        <v>1.3286</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.75</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1899,25 +1854,25 @@
         <v>65</v>
       </c>
       <c r="C13">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D13">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E13">
-        <v>-130</v>
+        <v>-170</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
       </c>
       <c r="G13">
-        <v>824394</v>
+        <v>822937</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1929,43 +1884,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2513</v>
+        <v>0.2628</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="P13">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="Q13">
-        <v>0.2667</v>
+        <v>0.307</v>
       </c>
       <c r="R13">
-        <v>0.375</v>
+        <v>0.363</v>
       </c>
       <c r="S13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T13">
-        <v>0.2077</v>
+        <v>0.1936</v>
       </c>
       <c r="U13">
-        <v>0.2074</v>
+        <v>0.1791</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2287</v>
+        <v>0.1898</v>
       </c>
       <c r="X13">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y13">
-        <v>0.9993</v>
+        <v>0.9933</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1974,22 +1929,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>5.71</v>
+        <v>5.33</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2571</v>
+        <v>0.2789</v>
       </c>
       <c r="AG13">
-        <v>0.9446</v>
+        <v>0.8746</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>5.71</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2000,25 +1955,25 @@
         <v>67</v>
       </c>
       <c r="C14">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D14">
         <v>-107</v>
       </c>
       <c r="E14">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>822937</v>
+      </c>
+      <c r="H14" t="s">
         <v>68</v>
       </c>
-      <c r="G14">
-        <v>824476</v>
-      </c>
-      <c r="H14" t="s">
-        <v>42</v>
-      </c>
       <c r="I14">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2030,43 +1985,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.2235</v>
+        <v>0.1713</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="P14">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="Q14">
-        <v>0.2617</v>
+        <v>0.2165</v>
       </c>
       <c r="R14">
-        <v>0.349</v>
+        <v>0.327</v>
       </c>
       <c r="S14" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2676</v>
+        <v>0.1894</v>
       </c>
       <c r="U14">
-        <v>0.2718</v>
+        <v>0.1807</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2505</v>
+        <v>0.1884</v>
       </c>
       <c r="X14">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y14">
-        <v>1.0326</v>
+        <v>0.88</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2075,22 +2030,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>6.43</v>
+        <v>2.54</v>
       </c>
       <c r="AE14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2368</v>
+        <v>0.186</v>
       </c>
       <c r="AG14">
-        <v>1.2168</v>
+        <v>0.8556</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>6.43</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2104,22 +2059,22 @@
         <v>6.5</v>
       </c>
       <c r="D15">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E15">
         <v>-130</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G15">
-        <v>824476</v>
+        <v>824394</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2131,43 +2086,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2871</v>
+        <v>0.2513</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P15">
-        <v>4.02</v>
+        <v>3.97</v>
       </c>
       <c r="Q15">
-        <v>0.292</v>
+        <v>0.2667</v>
       </c>
       <c r="R15">
-        <v>0.361</v>
+        <v>0.375</v>
       </c>
       <c r="S15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T15">
-        <v>0.1971</v>
+        <v>0.2077</v>
       </c>
       <c r="U15">
-        <v>0.1959</v>
+        <v>0.2074</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>0.2131</v>
+        <v>0.2287</v>
       </c>
       <c r="X15">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y15">
-        <v>0.9429</v>
+        <v>0.9993</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2176,22 +2131,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.58</v>
+        <v>5.67</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2889</v>
+        <v>0.2571</v>
       </c>
       <c r="AG15">
-        <v>0.8966</v>
+        <v>0.9381</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.58</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2199,28 +2154,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D16">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="E16">
-        <v>-107</v>
+        <v>-101</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G16">
-        <v>822937</v>
+        <v>823748</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I16">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2232,43 +2187,43 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>0.1713</v>
+        <v>0.2662</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="P16">
-        <v>4.41</v>
+        <v>3.93</v>
       </c>
       <c r="Q16">
-        <v>0.2165</v>
+        <v>0.2705</v>
       </c>
       <c r="R16">
-        <v>0.327</v>
+        <v>0.379</v>
       </c>
       <c r="S16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T16">
-        <v>0.1771</v>
+        <v>0.2278</v>
       </c>
       <c r="U16">
-        <v>0.1754</v>
+        <v>0.2279</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>0.1884</v>
+        <v>0.2141</v>
       </c>
       <c r="X16">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y16">
-        <v>0.9042</v>
+        <v>1.0015</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2277,22 +2232,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>2.45</v>
+        <v>6.57</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF16">
-        <v>0.186</v>
+        <v>0.2678</v>
       </c>
       <c r="AG16">
-        <v>0.8056</v>
+        <v>1.0289</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>2.45</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2306,22 +2261,22 @@
         <v>5.5</v>
       </c>
       <c r="D17">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="E17">
-        <v>-155</v>
+        <v>-135</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G17">
-        <v>822937</v>
+        <v>823748</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2333,43 +2288,43 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2628</v>
+        <v>0.2308</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P17">
-        <v>3.91</v>
+        <v>4.16</v>
       </c>
       <c r="Q17">
-        <v>0.307</v>
+        <v>0.2373</v>
       </c>
       <c r="R17">
-        <v>0.363</v>
+        <v>0.371</v>
       </c>
       <c r="S17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T17">
-        <v>0.1936</v>
+        <v>0.2159</v>
       </c>
       <c r="U17">
-        <v>0.1791</v>
+        <v>0.2005</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.1898</v>
+        <v>0.2245</v>
       </c>
       <c r="X17">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y17">
-        <v>0.9933</v>
+        <v>0.9945</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2378,22 +2333,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>5.37</v>
+        <v>4.98</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.2789</v>
+        <v>0.2332</v>
       </c>
       <c r="AG17">
-        <v>0.8806</v>
+        <v>0.975</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>5.37</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2404,25 +2359,25 @@
         <v>74</v>
       </c>
       <c r="C18">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-108</v>
+        <v>132</v>
       </c>
       <c r="E18">
-        <v>-115</v>
+        <v>-160</v>
       </c>
       <c r="F18" t="s">
         <v>75</v>
       </c>
       <c r="G18">
-        <v>823748</v>
+        <v>824076</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2434,43 +2389,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2662</v>
+        <v>0.1821</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P18">
-        <v>3.93</v>
+        <v>4.26</v>
       </c>
       <c r="Q18">
-        <v>0.2705</v>
+        <v>0.1583</v>
       </c>
       <c r="R18">
-        <v>0.379</v>
+        <v>0.375</v>
       </c>
       <c r="S18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T18">
-        <v>0.2278</v>
+        <v>0.2407</v>
       </c>
       <c r="U18">
-        <v>0.2279</v>
+        <v>0.206</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2141</v>
+        <v>0.2132</v>
       </c>
       <c r="X18">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y18">
-        <v>1.0015</v>
+        <v>1.0264</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2479,22 +2434,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>6.61</v>
+        <v>4.58</v>
       </c>
       <c r="AE18" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.2678</v>
+        <v>0.1732</v>
       </c>
       <c r="AG18">
-        <v>1.036</v>
+        <v>1.087</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>6.61</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2505,25 +2460,25 @@
         <v>76</v>
       </c>
       <c r="C19">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>110</v>
+        <v>-106</v>
       </c>
       <c r="E19">
-        <v>-125</v>
+        <v>-106</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19">
-        <v>823748</v>
+        <v>822860</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2535,43 +2490,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2308</v>
+        <v>0.2095</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P19">
-        <v>4.16</v>
+        <v>4.36</v>
       </c>
       <c r="Q19">
-        <v>0.2373</v>
+        <v>0.2241</v>
       </c>
       <c r="R19">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="S19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T19">
-        <v>0.2159</v>
+        <v>0.2087</v>
       </c>
       <c r="U19">
-        <v>0.2005</v>
+        <v>0.2149</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2245</v>
+        <v>0.2078</v>
       </c>
       <c r="X19">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y19">
-        <v>0.9945</v>
+        <v>1.0169</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2580,22 +2535,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.02</v>
+        <v>4.42</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2332</v>
+        <v>0.2149</v>
       </c>
       <c r="AG19">
-        <v>0.9817</v>
+        <v>0.9427</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.02</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2603,19 +2558,19 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20">
         <v>5.5</v>
       </c>
       <c r="D20">
-        <v>-120</v>
+        <v>-136</v>
       </c>
       <c r="E20">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G20">
         <v>822860</v>
@@ -2654,7 +2609,7 @@
         <v>0.383</v>
       </c>
       <c r="S20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T20">
         <v>0.2166</v>
@@ -2669,7 +2624,7 @@
         <v>0.222</v>
       </c>
       <c r="X20">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y20">
         <v>1.0062</v>
@@ -2681,7 +2636,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2690,13 +2645,13 @@
         <v>0.26</v>
       </c>
       <c r="AG20">
-        <v>0.9852</v>
+        <v>0.9784</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2710,70 +2665,28 @@
         <v>4.5</v>
       </c>
       <c r="D21">
-        <v>-125</v>
+        <v>-114</v>
       </c>
       <c r="E21">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21">
-        <v>822860</v>
+        <v>80</v>
+      </c>
+      <c r="G21" t="s">
+        <v>44</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
-      </c>
-      <c r="I21">
-        <v>4.9</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L21">
         <v>6</v>
       </c>
-      <c r="M21">
-        <v>0.2095</v>
-      </c>
-      <c r="N21">
-        <v>5</v>
-      </c>
-      <c r="O21">
-        <v>116</v>
-      </c>
-      <c r="P21">
-        <v>4.36</v>
-      </c>
-      <c r="Q21">
-        <v>0.2241</v>
-      </c>
-      <c r="R21">
-        <v>0.367</v>
-      </c>
       <c r="S21" t="s">
-        <v>58</v>
-      </c>
-      <c r="T21">
-        <v>0.2087</v>
-      </c>
-      <c r="U21">
-        <v>0.2149</v>
-      </c>
-      <c r="V21">
-        <v>9</v>
-      </c>
-      <c r="W21">
-        <v>0.2078</v>
-      </c>
-      <c r="X21">
-        <v>0.2199</v>
-      </c>
-      <c r="Y21">
-        <v>1.0169</v>
+        <v>44</v>
+      </c>
+      <c r="V21" t="s">
+        <v>44</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2781,23 +2694,8 @@
       <c r="AC21" t="s">
         <v>44</v>
       </c>
-      <c r="AD21">
-        <v>4.45</v>
-      </c>
       <c r="AE21" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF21">
-        <v>0.2149</v>
-      </c>
-      <c r="AG21">
-        <v>0.9493</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>4.45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2805,13 +2703,22 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="C22">
+        <v>4.5</v>
+      </c>
+      <c r="D22">
+        <v>-150</v>
+      </c>
+      <c r="E22">
+        <v>124</v>
       </c>
       <c r="F22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G22">
-        <v>824155</v>
+        <v>824318</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
@@ -2826,46 +2733,46 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2222</v>
+        <v>0.2293</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="P22">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="Q22">
-        <v>0.2286</v>
+        <v>0.2353</v>
       </c>
       <c r="R22">
-        <v>0.344</v>
+        <v>0.373</v>
       </c>
       <c r="S22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T22">
-        <v>0.2069</v>
+        <v>0.2228</v>
       </c>
       <c r="U22">
-        <v>0.1979</v>
+        <v>0.2203</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2173</v>
+        <v>0.2167</v>
       </c>
       <c r="X22">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y22">
-        <v>0.9851</v>
+        <v>1.0193</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2874,22 +2781,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.7</v>
+        <v>5.33</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2244</v>
+        <v>0.2315</v>
       </c>
       <c r="AG22">
-        <v>0.9407</v>
+        <v>1.0063</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>4.7</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2897,19 +2804,19 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23">
+        <v>3.5</v>
+      </c>
+      <c r="D23">
+        <v>-130</v>
+      </c>
+      <c r="E23">
+        <v>115</v>
+      </c>
+      <c r="F23" t="s">
         <v>82</v>
-      </c>
-      <c r="C23">
-        <v>4.5</v>
-      </c>
-      <c r="D23">
-        <v>-142</v>
-      </c>
-      <c r="E23">
-        <v>124</v>
-      </c>
-      <c r="F23" t="s">
-        <v>83</v>
       </c>
       <c r="G23">
         <v>824318</v>
@@ -2918,7 +2825,7 @@
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2927,46 +2834,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2293</v>
+        <v>0.1828</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="P23">
-        <v>4.24</v>
+        <v>4.44</v>
       </c>
       <c r="Q23">
-        <v>0.2353</v>
+        <v>0.1418</v>
       </c>
       <c r="R23">
-        <v>0.373</v>
+        <v>0.401</v>
       </c>
       <c r="S23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T23">
-        <v>0.2228</v>
+        <v>0.2756</v>
       </c>
       <c r="U23">
-        <v>0.2203</v>
+        <v>0.21</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2167</v>
+        <v>0.2007</v>
       </c>
       <c r="X23">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y23">
-        <v>1.0193</v>
+        <v>0.9927</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2975,22 +2882,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2315</v>
+        <v>0.1664</v>
       </c>
       <c r="AG23">
-        <v>1.0132</v>
+        <v>1.2448</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3001,25 +2908,25 @@
         <v>84</v>
       </c>
       <c r="C24">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D24">
-        <v>-130</v>
+        <v>136</v>
       </c>
       <c r="E24">
-        <v>115</v>
+        <v>-162</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G24">
-        <v>824318</v>
+        <v>823342</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3031,43 +2938,43 @@
         <v>5</v>
       </c>
       <c r="M24">
-        <v>0.1828</v>
+        <v>0.2984</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="P24">
-        <v>4.44</v>
+        <v>4.12</v>
       </c>
       <c r="Q24">
-        <v>0.1418</v>
+        <v>0.3056</v>
       </c>
       <c r="R24">
-        <v>0.401</v>
+        <v>0.351</v>
       </c>
       <c r="S24" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2756</v>
+        <v>0.183</v>
       </c>
       <c r="U24">
-        <v>0.21</v>
+        <v>0.1827</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2007</v>
+        <v>0.2228</v>
       </c>
       <c r="X24">
-        <v>0.2199</v>
+        <v>0.2214</v>
       </c>
       <c r="Y24">
-        <v>0.9927</v>
+        <v>0.9157</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3076,22 +2983,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.04</v>
+        <v>5.02</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.1664</v>
+        <v>0.3009</v>
       </c>
       <c r="AG24">
-        <v>1.2534</v>
+        <v>0.8263</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>5.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3099,34 +3006,76 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D25">
-        <v>104</v>
+        <v>-139</v>
       </c>
       <c r="E25">
-        <v>-117</v>
+        <v>120</v>
       </c>
       <c r="F25" t="s">
         <v>41</v>
       </c>
-      <c r="G25" t="s">
-        <v>44</v>
+      <c r="G25">
+        <v>823587</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>68</v>
+      </c>
+      <c r="I25">
+        <v>4.2</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
       </c>
       <c r="L25">
         <v>6</v>
       </c>
+      <c r="M25">
+        <v>0.2346</v>
+      </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
+      <c r="O25">
+        <v>81</v>
+      </c>
+      <c r="P25">
+        <v>4.8</v>
+      </c>
+      <c r="Q25">
+        <v>0.2346</v>
+      </c>
+      <c r="R25">
+        <v>0.288</v>
+      </c>
       <c r="S25" t="s">
-        <v>44</v>
-      </c>
-      <c r="V25" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T25">
+        <v>0.187</v>
+      </c>
+      <c r="U25">
+        <v>0.1827</v>
+      </c>
+      <c r="V25">
+        <v>9</v>
+      </c>
+      <c r="W25">
+        <v>0.2161</v>
+      </c>
+      <c r="X25">
+        <v>0.2214</v>
+      </c>
+      <c r="Y25">
+        <v>1.0272</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3134,8 +3083,23 @@
       <c r="AC25" t="s">
         <v>44</v>
       </c>
+      <c r="AD25">
+        <v>4.07</v>
+      </c>
       <c r="AE25" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF25">
+        <v>0.2346</v>
+      </c>
+      <c r="AG25">
+        <v>0.8448</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>4.07</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3143,34 +3107,76 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D26">
-        <v>-139</v>
+        <v>-132</v>
       </c>
       <c r="E26">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s">
         <v>47</v>
       </c>
-      <c r="G26" t="s">
-        <v>44</v>
+      <c r="G26">
+        <v>823664</v>
       </c>
       <c r="H26" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I26">
+        <v>5.6</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="M26">
+        <v>0.2638</v>
+      </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26">
+        <v>117</v>
+      </c>
+      <c r="P26">
+        <v>4.26</v>
+      </c>
+      <c r="Q26">
+        <v>0.2393</v>
+      </c>
+      <c r="R26">
+        <v>0.369</v>
       </c>
       <c r="S26" t="s">
-        <v>44</v>
-      </c>
-      <c r="V26" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T26">
+        <v>0.2362</v>
+      </c>
+      <c r="U26">
+        <v>0.2336</v>
+      </c>
+      <c r="V26">
+        <v>9</v>
+      </c>
+      <c r="W26">
+        <v>0.2177</v>
+      </c>
+      <c r="X26">
+        <v>0.2214</v>
+      </c>
+      <c r="Y26">
+        <v>1.0473</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3178,8 +3184,23 @@
       <c r="AC26" t="s">
         <v>44</v>
       </c>
+      <c r="AD26">
+        <v>6.82</v>
+      </c>
       <c r="AE26" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AF26">
+        <v>0.2547</v>
+      </c>
+      <c r="AG26">
+        <v>1.0669</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>6.82</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3187,34 +3208,67 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27">
-        <v>4.5</v>
-      </c>
-      <c r="D27">
-        <v>132</v>
-      </c>
-      <c r="E27">
-        <v>-165</v>
+        <v>88</v>
       </c>
       <c r="F27" t="s">
         <v>49</v>
       </c>
-      <c r="G27" t="s">
-        <v>44</v>
+      <c r="G27">
+        <v>824640</v>
       </c>
       <c r="H27" t="s">
-        <v>44</v>
+        <v>89</v>
+      </c>
+      <c r="I27">
+        <v>2.1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0.2261</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
+        <v>21</v>
+      </c>
+      <c r="P27">
+        <v>4.04</v>
+      </c>
+      <c r="Q27">
+        <v>0.2857</v>
+      </c>
+      <c r="R27">
+        <v>0.095</v>
       </c>
       <c r="S27" t="s">
-        <v>44</v>
-      </c>
-      <c r="V27" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T27">
+        <v>0.2115</v>
+      </c>
+      <c r="U27">
+        <v>0.2131</v>
+      </c>
+      <c r="V27">
+        <v>9</v>
+      </c>
+      <c r="W27">
+        <v>0.2191</v>
+      </c>
+      <c r="X27">
+        <v>0.2214</v>
+      </c>
+      <c r="Y27">
+        <v>0.8952</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3222,8 +3276,23 @@
       <c r="AC27" t="s">
         <v>44</v>
       </c>
+      <c r="AD27">
+        <v>1.69</v>
+      </c>
       <c r="AE27" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF27">
+        <v>0.2318</v>
+      </c>
+      <c r="AG27">
+        <v>0.9552</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>1.69</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3231,34 +3300,67 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28">
-        <v>4.5</v>
-      </c>
-      <c r="D28">
-        <v>128</v>
-      </c>
-      <c r="E28">
-        <v>-122</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" t="s">
-        <v>44</v>
+        <v>80</v>
+      </c>
+      <c r="G28">
+        <v>824155</v>
       </c>
       <c r="H28" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I28">
+        <v>5.3</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0.2222</v>
+      </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
+      <c r="O28">
+        <v>105</v>
+      </c>
+      <c r="P28">
+        <v>4.26</v>
+      </c>
+      <c r="Q28">
+        <v>0.2286</v>
+      </c>
+      <c r="R28">
+        <v>0.344</v>
       </c>
       <c r="S28" t="s">
-        <v>44</v>
-      </c>
-      <c r="V28" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="T28">
+        <v>0.2069</v>
+      </c>
+      <c r="U28">
+        <v>0.1979</v>
+      </c>
+      <c r="V28">
+        <v>8</v>
+      </c>
+      <c r="W28">
+        <v>0.2173</v>
+      </c>
+      <c r="X28">
+        <v>0.2214</v>
+      </c>
+      <c r="Y28">
+        <v>0.9851</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3266,8 +3368,23 @@
       <c r="AC28" t="s">
         <v>44</v>
       </c>
+      <c r="AD28">
+        <v>4.67</v>
+      </c>
       <c r="AE28" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF28">
+        <v>0.2244</v>
+      </c>
+      <c r="AG28">
+        <v>0.9343</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>4.67</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3275,19 +3392,19 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C29">
         <v>4.5</v>
       </c>
       <c r="D29">
-        <v>-114</v>
+        <v>104</v>
       </c>
       <c r="E29">
-        <v>105</v>
+        <v>-117</v>
       </c>
       <c r="F29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G29" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-19.xlsx
+++ b/data/k-props/2026-08-19.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="93">
   <si>
     <t>date</t>
   </si>
@@ -133,157 +133,160 @@
     <t>08/19/2026</t>
   </si>
   <si>
+    <t>Brandon Pfaadt</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Aaron Nola</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Chris Bassitt</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Will Warren</t>
+  </si>
+  <si>
+    <t>Chase Burns</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Matthew Liberatore</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Drew Rasmussen</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Max Scherzer</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Logan Gilbert</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Dustin May</t>
+  </si>
+  <si>
+    <t>Seth Lugo</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Jeffrey Springs</t>
+  </si>
+  <si>
+    <t>Kumar Rocker</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Walbert Urena</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Roki Sasaki</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Kyle Freeland</t>
+  </si>
+  <si>
+    <t>Paul Skenes</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Pittsburgh Pirates</t>
+  </si>
+  <si>
     <t>Michael King</t>
   </si>
   <si>
     <t>San Diego Padres @ New York Mets</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
+    <t>Robert Stock</t>
+  </si>
+  <si>
+    <t>Taj Bradley</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Sean Newcomb</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Clay Holmes</t>
+  </si>
+  <si>
+    <t>Payton Tolle</t>
+  </si>
+  <si>
+    <t>Walbert Ureña</t>
   </si>
   <si>
     <t>AJ Smith-Shawver</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Clay Holmes</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Payton Tolle</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Brandon Pfaadt</t>
-  </si>
-  <si>
-    <t>Aaron Nola</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
-  </si>
-  <si>
-    <t>Chris Bassitt</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Will Warren</t>
-  </si>
-  <si>
-    <t>Chase Burns</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Matthew Liberatore</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Drew Rasmussen</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Max Scherzer</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Parker Messick</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Logan Gilbert</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Dustin May</t>
-  </si>
-  <si>
-    <t>Seth Lugo</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Kumar Rocker</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
-  </si>
-  <si>
-    <t>Walbert Urena</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Roki Sasaki</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Kyle Freeland</t>
-  </si>
-  <si>
-    <t>Paul Skenes</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Robert Stock</t>
-  </si>
-  <si>
-    <t>Taj Bradley</t>
-  </si>
-  <si>
-    <t>Sean Newcomb</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Walbert Ureña</t>
   </si>
   <si>
     <t>Jackson Jobe</t>
@@ -667,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM29"/>
+  <dimension ref="A1:AM30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -800,25 +803,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="D2">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E2">
-        <v>-165</v>
+        <v>-185</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823587</v>
+        <v>824722</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -830,43 +833,43 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>0.2112</v>
+        <v>0.1713</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P2">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="Q2">
-        <v>0.2193</v>
+        <v>0.1983</v>
       </c>
       <c r="R2">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.236</v>
+        <v>0.1864</v>
       </c>
       <c r="U2">
-        <v>0.2368</v>
+        <v>0.1979</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2253</v>
+        <v>0.215</v>
       </c>
       <c r="X2">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y2">
-        <v>0.9921</v>
+        <v>1.0088</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -875,22 +878,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>5.28</v>
+        <v>3.67</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2142</v>
+        <v>0.1812</v>
       </c>
       <c r="AG2">
-        <v>1.0658</v>
+        <v>0.8454</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>5.28</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -901,31 +904,73 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3">
-        <v>-245</v>
+        <v>-124</v>
       </c>
       <c r="E3">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="F3" t="s">
         <v>47</v>
       </c>
-      <c r="G3" t="s">
-        <v>44</v>
+      <c r="G3">
+        <v>823424</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I3">
+        <v>5.2</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>0.2434</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>115</v>
+      </c>
+      <c r="P3">
+        <v>4.36</v>
+      </c>
+      <c r="Q3">
+        <v>0.2609</v>
+      </c>
+      <c r="R3">
+        <v>0.365</v>
       </c>
       <c r="S3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T3">
+        <v>0.2385</v>
+      </c>
+      <c r="U3">
+        <v>0.2228</v>
+      </c>
+      <c r="V3">
+        <v>9</v>
+      </c>
+      <c r="W3">
+        <v>0.2119</v>
+      </c>
+      <c r="X3">
+        <v>0.2205</v>
+      </c>
+      <c r="Y3">
+        <v>0.9512</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -933,8 +978,23 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
+      <c r="AD3">
+        <v>5.83</v>
+      </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF3">
+        <v>0.2498</v>
+      </c>
+      <c r="AG3">
+        <v>1.0815</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>5.83</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -945,25 +1005,25 @@
         <v>48</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D4">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4">
-        <v>-170</v>
+        <v>-145</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G4">
-        <v>824640</v>
+        <v>823424</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -972,46 +1032,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>0.1842</v>
+        <v>0.1852</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="P4">
-        <v>4.03</v>
+        <v>4.11</v>
       </c>
       <c r="Q4">
-        <v>0.1895</v>
+        <v>0.1716</v>
       </c>
       <c r="R4">
-        <v>0.322</v>
+        <v>0.401</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.248</v>
+        <v>0.1831</v>
       </c>
       <c r="U4">
-        <v>0.2503</v>
+        <v>0.1751</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2364</v>
+        <v>0.2232</v>
       </c>
       <c r="X4">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y4">
-        <v>1.0504</v>
+        <v>0.9247</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1020,22 +1080,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.85</v>
+        <v>3.73</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1859</v>
+        <v>0.1798</v>
       </c>
       <c r="AG4">
-        <v>1.1199</v>
+        <v>0.8303</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>4.85</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1043,28 +1103,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+      <c r="D5">
+        <v>-113</v>
+      </c>
+      <c r="E5">
+        <v>-107</v>
+      </c>
+      <c r="F5" t="s">
         <v>50</v>
       </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-      <c r="D5">
-        <v>-120</v>
-      </c>
-      <c r="E5">
-        <v>102</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
       <c r="G5">
-        <v>824722</v>
+        <v>824801</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1073,46 +1133,46 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>0.2777</v>
+        <v>0.1404</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="P5">
-        <v>4.01</v>
+        <v>4.62</v>
       </c>
       <c r="Q5">
-        <v>0.3417</v>
+        <v>0.1215</v>
       </c>
       <c r="R5">
-        <v>0.375</v>
+        <v>0.349</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2328</v>
+        <v>0.2613</v>
       </c>
       <c r="U5">
-        <v>0.1756</v>
+        <v>0.2658</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.1747</v>
+        <v>0.2463</v>
       </c>
       <c r="X5">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y5">
-        <v>0.88</v>
+        <v>1.0657</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1121,22 +1181,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.43</v>
+        <v>3.64</v>
       </c>
       <c r="AE5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.3017</v>
+        <v>0.1338</v>
       </c>
       <c r="AG5">
-        <v>1.0514</v>
+        <v>1.185</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>6.43</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1144,28 +1204,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C6">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D6">
-        <v>-114</v>
+        <v>120</v>
       </c>
       <c r="E6">
-        <v>-104</v>
+        <v>-147</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>824722</v>
+        <v>824801</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1174,46 +1234,46 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>0.1609</v>
+        <v>0.2263</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="P6">
-        <v>4.09</v>
+        <v>4.38</v>
       </c>
       <c r="Q6">
-        <v>0.136</v>
+        <v>0.2136</v>
       </c>
       <c r="R6">
-        <v>0.385</v>
+        <v>0.34</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.1864</v>
+        <v>0.2335</v>
       </c>
       <c r="U6">
-        <v>0.1979</v>
+        <v>0.2465</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.215</v>
+        <v>0.2369</v>
       </c>
       <c r="X6">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y6">
-        <v>1.0088</v>
+        <v>1.0727</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1222,22 +1282,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.13</v>
+        <v>5.64</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.1514</v>
+        <v>0.222</v>
       </c>
       <c r="AG6">
-        <v>0.8419</v>
+        <v>1.059</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>3.13</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1245,28 +1305,28 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D7">
-        <v>-124</v>
+        <v>112</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>-134</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>823424</v>
+        <v>824476</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
       <c r="I7">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1275,46 +1335,46 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>0.2434</v>
+        <v>0.2871</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P7">
-        <v>4.36</v>
+        <v>4.02</v>
       </c>
       <c r="Q7">
-        <v>0.2609</v>
+        <v>0.292</v>
       </c>
       <c r="R7">
-        <v>0.365</v>
+        <v>0.361</v>
       </c>
       <c r="S7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2331</v>
+        <v>0.2089</v>
       </c>
       <c r="U7">
-        <v>0.2217</v>
+        <v>0.2069</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2119</v>
+        <v>0.2131</v>
       </c>
       <c r="X7">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y7">
-        <v>0.987</v>
+        <v>0.8863</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1323,22 +1383,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>5.89</v>
+        <v>5.55</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.2498</v>
+        <v>0.2889</v>
       </c>
       <c r="AG7">
-        <v>1.0529</v>
+        <v>0.9472</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>5.89</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1346,28 +1406,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D8">
-        <v>126</v>
+        <v>-114</v>
       </c>
       <c r="E8">
-        <v>-145</v>
+        <v>-104</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G8">
-        <v>823424</v>
+        <v>824476</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1376,46 +1436,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1852</v>
+        <v>0.2235</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="P8">
-        <v>4.11</v>
+        <v>4.36</v>
       </c>
       <c r="Q8">
-        <v>0.1716</v>
+        <v>0.2617</v>
       </c>
       <c r="R8">
-        <v>0.401</v>
+        <v>0.349</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.1831</v>
+        <v>0.2942</v>
       </c>
       <c r="U8">
-        <v>0.1751</v>
+        <v>0.2795</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2232</v>
+        <v>0.2505</v>
       </c>
       <c r="X8">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y8">
-        <v>0.9247</v>
+        <v>1.0673</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1424,22 +1484,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.71</v>
+        <v>7.29</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AF8">
-        <v>0.1798</v>
+        <v>0.2368</v>
       </c>
       <c r="AG8">
-        <v>0.8269</v>
+        <v>1.3341</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.71</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1447,28 +1507,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D9">
-        <v>-113</v>
+        <v>115</v>
       </c>
       <c r="E9">
-        <v>-110</v>
+        <v>-137</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G9">
-        <v>824801</v>
+        <v>822937</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1477,46 +1537,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>0.1404</v>
+        <v>0.2628</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="P9">
-        <v>4.62</v>
+        <v>3.91</v>
       </c>
       <c r="Q9">
-        <v>0.1215</v>
+        <v>0.307</v>
       </c>
       <c r="R9">
-        <v>0.349</v>
+        <v>0.363</v>
       </c>
       <c r="S9" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2771</v>
+        <v>0.2319</v>
       </c>
       <c r="U9">
-        <v>0.2738</v>
+        <v>0.2142</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2463</v>
+        <v>0.1898</v>
       </c>
       <c r="X9">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y9">
-        <v>1.0317</v>
+        <v>1.0855</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1525,22 +1585,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.73</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>0.1338</v>
+        <v>0.2789</v>
       </c>
       <c r="AG9">
-        <v>1.2514</v>
+        <v>1.0516</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1548,28 +1608,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C10">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D10">
-        <v>122</v>
+        <v>-110</v>
       </c>
       <c r="E10">
-        <v>-150</v>
+        <v>-109</v>
       </c>
       <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10">
+        <v>822937</v>
+      </c>
+      <c r="H10" t="s">
         <v>59</v>
       </c>
-      <c r="G10">
-        <v>824801</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
       <c r="I10">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1581,43 +1641,43 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2263</v>
+        <v>0.1713</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="P10">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="Q10">
-        <v>0.2136</v>
+        <v>0.2165</v>
       </c>
       <c r="R10">
-        <v>0.34</v>
+        <v>0.327</v>
       </c>
       <c r="S10" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2209</v>
+        <v>0.1894</v>
       </c>
       <c r="U10">
-        <v>0.2383</v>
+        <v>0.1807</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2369</v>
+        <v>0.1884</v>
       </c>
       <c r="X10">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y10">
-        <v>1.0332</v>
+        <v>0.88</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1626,22 +1686,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>5.11</v>
+        <v>2.55</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.222</v>
+        <v>0.186</v>
       </c>
       <c r="AG10">
-        <v>0.9976</v>
+        <v>0.8592</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>5.11</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1649,28 +1709,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>6.5</v>
       </c>
       <c r="D11">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E11">
         <v>-124</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>824476</v>
+        <v>824394</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1682,43 +1742,43 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2871</v>
+        <v>0.2513</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P11">
-        <v>4.02</v>
+        <v>3.97</v>
       </c>
       <c r="Q11">
-        <v>0.292</v>
+        <v>0.2667</v>
       </c>
       <c r="R11">
-        <v>0.361</v>
+        <v>0.375</v>
       </c>
       <c r="S11" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.1971</v>
+        <v>0.2335</v>
       </c>
       <c r="U11">
-        <v>0.1959</v>
+        <v>0.2204</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2131</v>
+        <v>0.2287</v>
       </c>
       <c r="X11">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y11">
-        <v>0.9429</v>
+        <v>1.0313</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1727,22 +1787,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.55</v>
+        <v>6.61</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="AF11">
-        <v>0.2889</v>
+        <v>0.2571</v>
       </c>
       <c r="AG11">
-        <v>0.8904</v>
+        <v>1.0589</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.55</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1753,25 +1813,25 @@
         <v>63</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D12">
-        <v>-115</v>
+        <v>112</v>
       </c>
       <c r="E12">
-        <v>-104</v>
+        <v>-137</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G12">
-        <v>824476</v>
+        <v>823748</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1783,43 +1843,43 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.2235</v>
+        <v>0.2662</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="P12">
-        <v>4.36</v>
+        <v>3.93</v>
       </c>
       <c r="Q12">
-        <v>0.2617</v>
+        <v>0.2705</v>
       </c>
       <c r="R12">
-        <v>0.349</v>
+        <v>0.379</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2942</v>
+        <v>0.2211</v>
       </c>
       <c r="U12">
-        <v>0.2795</v>
+        <v>0.2203</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2505</v>
+        <v>0.2141</v>
       </c>
       <c r="X12">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y12">
-        <v>1.0673</v>
+        <v>0.975</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1828,22 +1888,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>7.26</v>
+        <v>6.23</v>
       </c>
       <c r="AE12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AF12">
-        <v>0.2368</v>
+        <v>0.2678</v>
       </c>
       <c r="AG12">
-        <v>1.3286</v>
+        <v>1.0028</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>7.26</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1857,22 +1917,22 @@
         <v>5.5</v>
       </c>
       <c r="D13">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="E13">
-        <v>-170</v>
+        <v>-135</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G13">
-        <v>822937</v>
+        <v>823748</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1884,43 +1944,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2628</v>
+        <v>0.2308</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P13">
-        <v>3.91</v>
+        <v>4.16</v>
       </c>
       <c r="Q13">
-        <v>0.307</v>
+        <v>0.2373</v>
       </c>
       <c r="R13">
-        <v>0.363</v>
+        <v>0.371</v>
       </c>
       <c r="S13" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.1936</v>
+        <v>0.2105</v>
       </c>
       <c r="U13">
-        <v>0.1791</v>
+        <v>0.1973</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.1898</v>
+        <v>0.2245</v>
       </c>
       <c r="X13">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y13">
-        <v>0.9933</v>
+        <v>0.9742</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1929,22 +1989,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>5.33</v>
+        <v>4.78</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2789</v>
+        <v>0.2332</v>
       </c>
       <c r="AG13">
-        <v>0.8746</v>
+        <v>0.9549</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>5.33</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1952,28 +2012,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14">
+        <v>4.5</v>
+      </c>
+      <c r="D14">
+        <v>130</v>
+      </c>
+      <c r="E14">
+        <v>-150</v>
+      </c>
+      <c r="F14" t="s">
         <v>67</v>
       </c>
-      <c r="C14">
-        <v>3.5</v>
-      </c>
-      <c r="D14">
-        <v>-107</v>
-      </c>
-      <c r="E14">
-        <v>-113</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
       <c r="G14">
-        <v>822937</v>
+        <v>824076</v>
       </c>
       <c r="H14" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="I14">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1985,43 +2045,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1713</v>
+        <v>0.1821</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="P14">
-        <v>4.41</v>
+        <v>4.26</v>
       </c>
       <c r="Q14">
-        <v>0.2165</v>
+        <v>0.1583</v>
       </c>
       <c r="R14">
-        <v>0.327</v>
+        <v>0.375</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.1894</v>
+        <v>0.2016</v>
       </c>
       <c r="U14">
-        <v>0.1807</v>
+        <v>0.1918</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.1884</v>
+        <v>0.2132</v>
       </c>
       <c r="X14">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y14">
-        <v>0.88</v>
+        <v>1.0355</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2030,22 +2090,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>2.54</v>
+        <v>3.89</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.186</v>
+        <v>0.1732</v>
       </c>
       <c r="AG14">
-        <v>0.8556</v>
+        <v>0.9143</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>2.54</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2053,28 +2113,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D15">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E15">
-        <v>-130</v>
+        <v>-147</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G15">
-        <v>824394</v>
+        <v>824076</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2083,46 +2143,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>0.2513</v>
+        <v>0.1837</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>3.97</v>
+        <v>4.44</v>
       </c>
       <c r="Q15">
-        <v>0.2667</v>
+        <v>0.1</v>
       </c>
       <c r="R15">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="S15" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2077</v>
+        <v>0.2</v>
       </c>
       <c r="U15">
-        <v>0.2074</v>
+        <v>0.2033</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2287</v>
+        <v>0.2167</v>
       </c>
       <c r="X15">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y15">
-        <v>0.9993</v>
+        <v>0.9044</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2131,22 +2191,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.67</v>
+        <v>2.79</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2571</v>
+        <v>0.1562</v>
       </c>
       <c r="AG15">
-        <v>0.9381</v>
+        <v>0.9072</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.67</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2154,28 +2214,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C16">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D16">
-        <v>-115</v>
+        <v>110</v>
       </c>
       <c r="E16">
-        <v>-101</v>
+        <v>-118</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G16">
-        <v>823748</v>
+        <v>822860</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2187,43 +2247,43 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>0.2662</v>
+        <v>0.2095</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="P16">
-        <v>3.93</v>
+        <v>4.36</v>
       </c>
       <c r="Q16">
-        <v>0.2705</v>
+        <v>0.2241</v>
       </c>
       <c r="R16">
-        <v>0.379</v>
+        <v>0.367</v>
       </c>
       <c r="S16" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2278</v>
+        <v>0.2033</v>
       </c>
       <c r="U16">
-        <v>0.2279</v>
+        <v>0.2026</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2141</v>
+        <v>0.2078</v>
       </c>
       <c r="X16">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y16">
-        <v>1.0015</v>
+        <v>0.9473</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2232,22 +2292,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>6.57</v>
+        <v>4.03</v>
       </c>
       <c r="AE16" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.2678</v>
+        <v>0.2149</v>
       </c>
       <c r="AG16">
-        <v>1.0289</v>
+        <v>0.9219</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>6.57</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2255,22 +2315,22 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17">
         <v>5.5</v>
       </c>
       <c r="D17">
-        <v>120</v>
+        <v>-140</v>
       </c>
       <c r="E17">
-        <v>-135</v>
+        <v>125</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G17">
-        <v>823748</v>
+        <v>822860</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
@@ -2288,43 +2348,43 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2308</v>
+        <v>0.2612</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="P17">
-        <v>4.16</v>
+        <v>4.23</v>
       </c>
       <c r="Q17">
-        <v>0.2373</v>
+        <v>0.2581</v>
       </c>
       <c r="R17">
-        <v>0.371</v>
+        <v>0.383</v>
       </c>
       <c r="S17" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2159</v>
+        <v>0.2527</v>
       </c>
       <c r="U17">
-        <v>0.2005</v>
+        <v>0.2393</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2245</v>
+        <v>0.222</v>
       </c>
       <c r="X17">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y17">
-        <v>0.9945</v>
+        <v>1.0139</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2333,22 +2393,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.98</v>
+        <v>6.72</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="AF17">
-        <v>0.2332</v>
+        <v>0.26</v>
       </c>
       <c r="AG17">
-        <v>0.975</v>
+        <v>1.1461</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.98</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2356,76 +2416,34 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>4.5</v>
       </c>
       <c r="D18">
-        <v>132</v>
+        <v>-117</v>
       </c>
       <c r="E18">
-        <v>-160</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18">
-        <v>824076</v>
+        <v>73</v>
+      </c>
+      <c r="G18" t="s">
+        <v>44</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18">
-        <v>5.6</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
-      <c r="M18">
-        <v>0.1821</v>
-      </c>
-      <c r="N18">
-        <v>5</v>
-      </c>
-      <c r="O18">
-        <v>120</v>
-      </c>
-      <c r="P18">
-        <v>4.26</v>
-      </c>
-      <c r="Q18">
-        <v>0.1583</v>
-      </c>
-      <c r="R18">
-        <v>0.375</v>
-      </c>
       <c r="S18" t="s">
-        <v>56</v>
-      </c>
-      <c r="T18">
-        <v>0.2407</v>
-      </c>
-      <c r="U18">
-        <v>0.206</v>
-      </c>
-      <c r="V18">
-        <v>9</v>
-      </c>
-      <c r="W18">
-        <v>0.2132</v>
-      </c>
-      <c r="X18">
-        <v>0.2214</v>
-      </c>
-      <c r="Y18">
-        <v>1.0264</v>
+        <v>44</v>
+      </c>
+      <c r="V18" t="s">
+        <v>44</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2433,23 +2451,8 @@
       <c r="AC18" t="s">
         <v>44</v>
       </c>
-      <c r="AD18">
-        <v>4.58</v>
-      </c>
       <c r="AE18" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF18">
-        <v>0.1732</v>
-      </c>
-      <c r="AG18">
-        <v>1.087</v>
-      </c>
-      <c r="AH18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>4.58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2457,28 +2460,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>4.5</v>
       </c>
       <c r="D19">
-        <v>-106</v>
+        <v>-150</v>
       </c>
       <c r="E19">
-        <v>-106</v>
+        <v>126</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G19">
-        <v>822860</v>
+        <v>824318</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2490,43 +2493,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2095</v>
+        <v>0.2293</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="P19">
-        <v>4.36</v>
+        <v>4.24</v>
       </c>
       <c r="Q19">
-        <v>0.2241</v>
+        <v>0.2353</v>
       </c>
       <c r="R19">
-        <v>0.367</v>
+        <v>0.373</v>
       </c>
       <c r="S19" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="T19">
-        <v>0.2087</v>
+        <v>0.2228</v>
       </c>
       <c r="U19">
-        <v>0.2149</v>
+        <v>0.2203</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2078</v>
+        <v>0.2167</v>
       </c>
       <c r="X19">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y19">
-        <v>1.0169</v>
+        <v>1.0193</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2535,22 +2538,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.42</v>
+        <v>5.35</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2149</v>
+        <v>0.2315</v>
       </c>
       <c r="AG19">
-        <v>0.9427</v>
+        <v>1.0105</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.42</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2558,28 +2561,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D20">
         <v>-136</v>
       </c>
       <c r="E20">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G20">
-        <v>822860</v>
+        <v>824318</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2591,43 +2594,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2612</v>
+        <v>0.1828</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="P20">
-        <v>4.23</v>
+        <v>4.44</v>
       </c>
       <c r="Q20">
-        <v>0.2581</v>
+        <v>0.1418</v>
       </c>
       <c r="R20">
-        <v>0.383</v>
+        <v>0.401</v>
       </c>
       <c r="S20" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2166</v>
+        <v>0.2076</v>
       </c>
       <c r="U20">
-        <v>0.2336</v>
+        <v>0.1836</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.222</v>
+        <v>0.2007</v>
       </c>
       <c r="X20">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y20">
-        <v>1.0062</v>
+        <v>0.9455</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2636,22 +2639,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>5.69</v>
+        <v>3.61</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.26</v>
+        <v>0.1664</v>
       </c>
       <c r="AG20">
-        <v>0.9784</v>
+        <v>0.9417</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>5.69</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2659,34 +2662,76 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21">
+        <v>6.5</v>
+      </c>
+      <c r="D21">
+        <v>136</v>
+      </c>
+      <c r="E21">
+        <v>-162</v>
+      </c>
+      <c r="F21" t="s">
         <v>79</v>
       </c>
-      <c r="C21">
-        <v>4.5</v>
-      </c>
-      <c r="D21">
-        <v>-114</v>
-      </c>
-      <c r="E21">
-        <v>105</v>
-      </c>
-      <c r="F21" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" t="s">
-        <v>44</v>
+      <c r="G21">
+        <v>823342</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I21">
+        <v>5.3</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="M21">
+        <v>0.2984</v>
+      </c>
+      <c r="N21">
+        <v>5</v>
+      </c>
+      <c r="O21">
+        <v>108</v>
+      </c>
+      <c r="P21">
+        <v>4.12</v>
+      </c>
+      <c r="Q21">
+        <v>0.3056</v>
+      </c>
+      <c r="R21">
+        <v>0.351</v>
       </c>
       <c r="S21" t="s">
-        <v>44</v>
-      </c>
-      <c r="V21" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T21">
+        <v>0.183</v>
+      </c>
+      <c r="U21">
+        <v>0.1827</v>
+      </c>
+      <c r="V21">
+        <v>9</v>
+      </c>
+      <c r="W21">
+        <v>0.2231</v>
+      </c>
+      <c r="X21">
+        <v>0.2205</v>
+      </c>
+      <c r="Y21">
+        <v>0.9157</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2694,8 +2739,23 @@
       <c r="AC21" t="s">
         <v>44</v>
       </c>
+      <c r="AD21">
+        <v>5.04</v>
+      </c>
       <c r="AE21" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF21">
+        <v>0.3009</v>
+      </c>
+      <c r="AG21">
+        <v>0.8297</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>5.04</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2703,28 +2763,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C22">
         <v>4.5</v>
       </c>
       <c r="D22">
-        <v>-150</v>
+        <v>120</v>
       </c>
       <c r="E22">
-        <v>124</v>
+        <v>-165</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22">
-        <v>824318</v>
+        <v>823587</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2733,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>0.2293</v>
+        <v>0.2098</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -2745,34 +2805,34 @@
         <v>119</v>
       </c>
       <c r="P22">
-        <v>4.24</v>
+        <v>4.09</v>
       </c>
       <c r="Q22">
-        <v>0.2353</v>
+        <v>0.2101</v>
       </c>
       <c r="R22">
         <v>0.373</v>
       </c>
       <c r="S22" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2228</v>
+        <v>0.236</v>
       </c>
       <c r="U22">
-        <v>0.2203</v>
+        <v>0.2368</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2167</v>
+        <v>0.2245</v>
       </c>
       <c r="X22">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y22">
-        <v>1.0193</v>
+        <v>0.9921</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2781,22 +2841,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.33</v>
+        <v>5.23</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2315</v>
+        <v>0.2099</v>
       </c>
       <c r="AG22">
-        <v>1.0063</v>
+        <v>1.0702</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.33</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2804,28 +2864,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23">
         <v>3.5</v>
       </c>
       <c r="D23">
-        <v>-130</v>
+        <v>-139</v>
       </c>
       <c r="E23">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G23">
-        <v>824318</v>
+        <v>823587</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="I23">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2837,43 +2897,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.1828</v>
+        <v>0.2346</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="P23">
-        <v>4.44</v>
+        <v>4.8</v>
       </c>
       <c r="Q23">
-        <v>0.1418</v>
+        <v>0.2346</v>
       </c>
       <c r="R23">
-        <v>0.401</v>
+        <v>0.288</v>
       </c>
       <c r="S23" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2756</v>
+        <v>0.187</v>
       </c>
       <c r="U23">
-        <v>0.21</v>
+        <v>0.1827</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2007</v>
+        <v>0.217</v>
       </c>
       <c r="X23">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y23">
-        <v>0.9927</v>
+        <v>1.0272</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2882,22 +2942,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.01</v>
+        <v>4.09</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.1664</v>
+        <v>0.2346</v>
       </c>
       <c r="AG23">
-        <v>1.2448</v>
+        <v>0.8483</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>5.01</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2905,28 +2965,28 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24">
+        <v>5.5</v>
+      </c>
+      <c r="D24">
+        <v>-132</v>
+      </c>
+      <c r="E24">
+        <v>108</v>
+      </c>
+      <c r="F24" t="s">
         <v>84</v>
       </c>
-      <c r="C24">
-        <v>6.5</v>
-      </c>
-      <c r="D24">
-        <v>136</v>
-      </c>
-      <c r="E24">
-        <v>-162</v>
-      </c>
-      <c r="F24" t="s">
-        <v>85</v>
-      </c>
       <c r="G24">
-        <v>823342</v>
+        <v>823664</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2938,43 +2998,43 @@
         <v>5</v>
       </c>
       <c r="M24">
-        <v>0.2984</v>
+        <v>0.2638</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="P24">
-        <v>4.12</v>
+        <v>4.26</v>
       </c>
       <c r="Q24">
-        <v>0.3056</v>
+        <v>0.2458</v>
       </c>
       <c r="R24">
-        <v>0.351</v>
+        <v>0.371</v>
       </c>
       <c r="S24" t="s">
         <v>43</v>
       </c>
       <c r="T24">
-        <v>0.183</v>
+        <v>0.2362</v>
       </c>
       <c r="U24">
-        <v>0.1827</v>
+        <v>0.2336</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2228</v>
+        <v>0.22</v>
       </c>
       <c r="X24">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y24">
-        <v>0.9157</v>
+        <v>1.0473</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2983,22 +3043,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.02</v>
+        <v>6.91</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="AF24">
-        <v>0.3009</v>
+        <v>0.2571</v>
       </c>
       <c r="AG24">
-        <v>0.8263</v>
+        <v>1.0713</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>5.02</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3006,76 +3066,67 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s">
         <v>86</v>
       </c>
-      <c r="C25">
-        <v>3.5</v>
-      </c>
-      <c r="D25">
-        <v>-139</v>
-      </c>
-      <c r="E25">
-        <v>120</v>
-      </c>
-      <c r="F25" t="s">
-        <v>41</v>
-      </c>
       <c r="G25">
-        <v>823587</v>
+        <v>824640</v>
       </c>
       <c r="H25" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="I25">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>0.2346</v>
+        <v>0.2261</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="P25">
-        <v>4.8</v>
+        <v>4.04</v>
       </c>
       <c r="Q25">
-        <v>0.2346</v>
+        <v>0.2857</v>
       </c>
       <c r="R25">
-        <v>0.288</v>
+        <v>0.095</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.187</v>
+        <v>0.2115</v>
       </c>
       <c r="U25">
-        <v>0.1827</v>
+        <v>0.2131</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2161</v>
+        <v>0.2179</v>
       </c>
       <c r="X25">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y25">
-        <v>1.0272</v>
+        <v>0.8952</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3084,22 +3135,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.07</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.2346</v>
+        <v>0.2318</v>
       </c>
       <c r="AG25">
-        <v>0.8448</v>
+        <v>0.9591</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>4.07</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3107,28 +3158,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D26">
-        <v>-132</v>
+        <v>125</v>
       </c>
       <c r="E26">
-        <v>108</v>
+        <v>-170</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="G26">
-        <v>823664</v>
+        <v>824640</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3137,46 +3188,46 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M26">
-        <v>0.2638</v>
+        <v>0.1799</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="P26">
-        <v>4.26</v>
+        <v>4.05</v>
       </c>
       <c r="Q26">
-        <v>0.2393</v>
+        <v>0.1727</v>
       </c>
       <c r="R26">
-        <v>0.369</v>
+        <v>0.355</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2362</v>
+        <v>0.248</v>
       </c>
       <c r="U26">
-        <v>0.2336</v>
+        <v>0.2503</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2177</v>
+        <v>0.2352</v>
       </c>
       <c r="X26">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y26">
-        <v>1.0473</v>
+        <v>1.0504</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3185,22 +3236,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>6.82</v>
+        <v>4.85</v>
       </c>
       <c r="AE26" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.2547</v>
+        <v>0.1773</v>
       </c>
       <c r="AG26">
-        <v>1.0669</v>
+        <v>1.1246</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>6.82</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3208,67 +3259,76 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="C27">
+        <v>5.5</v>
+      </c>
+      <c r="D27">
+        <v>-120</v>
+      </c>
+      <c r="E27">
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G27">
-        <v>824640</v>
+        <v>824722</v>
       </c>
       <c r="H27" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="I27">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>0.2261</v>
+        <v>0.2774</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="P27">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="Q27">
-        <v>0.2857</v>
+        <v>0.3276</v>
       </c>
       <c r="R27">
-        <v>0.095</v>
+        <v>0.367</v>
       </c>
       <c r="S27" t="s">
         <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2115</v>
+        <v>0.2328</v>
       </c>
       <c r="U27">
-        <v>0.2131</v>
+        <v>0.1756</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2191</v>
+        <v>0.1747</v>
       </c>
       <c r="X27">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y27">
-        <v>0.8952</v>
+        <v>0.88</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3277,22 +3337,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>1.69</v>
+        <v>6.32</v>
       </c>
       <c r="AE27" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="AF27">
-        <v>0.2318</v>
+        <v>0.2958</v>
       </c>
       <c r="AG27">
-        <v>0.9552</v>
+        <v>1.0558</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>1.69</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3303,7 +3363,7 @@
         <v>90</v>
       </c>
       <c r="F28" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G28">
         <v>824155</v>
@@ -3342,25 +3402,25 @@
         <v>0.344</v>
       </c>
       <c r="S28" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T28">
-        <v>0.2069</v>
+        <v>0.2139</v>
       </c>
       <c r="U28">
-        <v>0.1979</v>
+        <v>0.2061</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>0.2173</v>
       </c>
       <c r="X28">
-        <v>0.2214</v>
+        <v>0.2205</v>
       </c>
       <c r="Y28">
-        <v>0.9851</v>
+        <v>0.9671</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3369,7 +3429,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.67</v>
+        <v>4.76</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3378,13 +3438,13 @@
         <v>0.2244</v>
       </c>
       <c r="AG28">
-        <v>0.9343</v>
+        <v>0.97</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.67</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3395,39 +3455,83 @@
         <v>91</v>
       </c>
       <c r="C29">
+        <v>3.5</v>
+      </c>
+      <c r="D29">
+        <v>-245</v>
+      </c>
+      <c r="E29">
+        <v>180</v>
+      </c>
+      <c r="F29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" t="s">
+        <v>44</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="S29" t="s">
+        <v>44</v>
+      </c>
+      <c r="V29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30">
         <v>4.5</v>
       </c>
-      <c r="D29">
+      <c r="D30">
         <v>104</v>
       </c>
-      <c r="E29">
+      <c r="E30">
         <v>-117</v>
       </c>
-      <c r="F29" t="s">
-        <v>85</v>
-      </c>
-      <c r="G29" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" t="s">
-        <v>44</v>
-      </c>
-      <c r="L29">
+      <c r="F30" t="s">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" t="s">
+        <v>44</v>
+      </c>
+      <c r="L30">
         <v>6</v>
       </c>
-      <c r="S29" t="s">
-        <v>44</v>
-      </c>
-      <c r="V29" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE29" t="s">
+      <c r="S30" t="s">
+        <v>44</v>
+      </c>
+      <c r="V30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE30" t="s">
         <v>44</v>
       </c>
     </row>

--- a/data/k-props/2026-08-19.xlsx
+++ b/data/k-props/2026-08-19.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>date</t>
   </si>
@@ -133,73 +133,118 @@
     <t>08/19/2026</t>
   </si>
   <si>
+    <t>Paul Skenes</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Michael King</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ New York Mets</t>
+  </si>
+  <si>
+    <t>Robert Stock</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Taj Bradley</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Sean Newcomb</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Clay Holmes</t>
+  </si>
+  <si>
     <t>Brandon Pfaadt</t>
   </si>
   <si>
     <t>Arizona Diamondbacks @ Boston Red Sox</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
+    <t>Payton Tolle</t>
+  </si>
+  <si>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
   </si>
   <si>
     <t>Aaron Nola</t>
   </si>
   <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
+    <t>Will Warren</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Baltimore Orioles</t>
   </si>
   <si>
     <t>Chris Bassitt</t>
   </si>
   <si>
-    <t>New York Yankees @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Will Warren</t>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Matthew Liberatore</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
   </si>
   <si>
     <t>Chase Burns</t>
   </si>
   <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Matthew Liberatore</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
+    <t>Max Scherzer</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
   </si>
   <si>
     <t>Drew Rasmussen</t>
   </si>
   <si>
-    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Max Scherzer</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Parker Messick</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>6-7</t>
+    <t>Jeffrey Springs</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Seth Lugo</t>
   </si>
   <si>
     <t>Logan Gilbert</t>
@@ -211,79 +256,31 @@
     <t>Dustin May</t>
   </si>
   <si>
-    <t>Seth Lugo</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Jeffrey Springs</t>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Texas Rangers</t>
   </si>
   <si>
     <t>Kumar Rocker</t>
   </si>
   <si>
-    <t>Washington Nationals @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
+    <t>Walbert Ureña</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Roki Sasaki</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Kyle Freeland</t>
   </si>
   <si>
     <t>Walbert Urena</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Roki Sasaki</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Kyle Freeland</t>
-  </si>
-  <si>
-    <t>Paul Skenes</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Michael King</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ New York Mets</t>
-  </si>
-  <si>
-    <t>Robert Stock</t>
-  </si>
-  <si>
-    <t>Taj Bradley</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Sean Newcomb</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Clay Holmes</t>
-  </si>
-  <si>
-    <t>Payton Tolle</t>
-  </si>
-  <si>
-    <t>Walbert Ureña</t>
   </si>
   <si>
     <t>AJ Smith-Shawver</t>
@@ -803,25 +800,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="D2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E2">
-        <v>-185</v>
+        <v>-162</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>824722</v>
+        <v>823342</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -830,46 +827,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>0.1713</v>
+        <v>0.2984</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="P2">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="Q2">
-        <v>0.1983</v>
+        <v>0.3056</v>
       </c>
       <c r="R2">
-        <v>0.367</v>
+        <v>0.351</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1864</v>
+        <v>0.183</v>
       </c>
       <c r="U2">
-        <v>0.1979</v>
+        <v>0.1827</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.215</v>
+        <v>0.2231</v>
       </c>
       <c r="X2">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y2">
-        <v>1.0088</v>
+        <v>0.9157</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -878,22 +875,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.67</v>
+        <v>5.04</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1812</v>
+        <v>0.3009</v>
       </c>
       <c r="AG2">
-        <v>0.8454</v>
+        <v>0.8294</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>3.67</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -904,25 +901,25 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-124</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>108</v>
+        <v>-165</v>
       </c>
       <c r="F3" t="s">
         <v>47</v>
       </c>
       <c r="G3">
-        <v>823424</v>
+        <v>823587</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -931,46 +928,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>0.2434</v>
+        <v>0.2098</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="P3">
-        <v>4.36</v>
+        <v>4.09</v>
       </c>
       <c r="Q3">
-        <v>0.2609</v>
+        <v>0.2101</v>
       </c>
       <c r="R3">
-        <v>0.365</v>
+        <v>0.373</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2385</v>
+        <v>0.236</v>
       </c>
       <c r="U3">
-        <v>0.2228</v>
+        <v>0.2368</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2119</v>
+        <v>0.2245</v>
       </c>
       <c r="X3">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y3">
-        <v>0.9512</v>
+        <v>0.9921</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -979,22 +976,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.83</v>
+        <v>5.23</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2498</v>
+        <v>0.2099</v>
       </c>
       <c r="AG3">
-        <v>1.0815</v>
+        <v>1.0697</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>5.83</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1005,25 +1002,25 @@
         <v>48</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>124</v>
+        <v>-139</v>
       </c>
       <c r="E4">
-        <v>-145</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
         <v>47</v>
       </c>
       <c r="G4">
-        <v>823424</v>
+        <v>823587</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1032,46 +1029,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>0.1852</v>
+        <v>0.2346</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="P4">
-        <v>4.11</v>
+        <v>4.8</v>
       </c>
       <c r="Q4">
-        <v>0.1716</v>
+        <v>0.2346</v>
       </c>
       <c r="R4">
-        <v>0.401</v>
+        <v>0.288</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.1831</v>
+        <v>0.187</v>
       </c>
       <c r="U4">
-        <v>0.1751</v>
+        <v>0.1827</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2232</v>
+        <v>0.217</v>
       </c>
       <c r="X4">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y4">
-        <v>0.9247</v>
+        <v>1.0272</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1080,22 +1077,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.73</v>
+        <v>4.09</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1798</v>
+        <v>0.2346</v>
       </c>
       <c r="AG4">
-        <v>0.8303</v>
+        <v>0.8479</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.73</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1103,28 +1100,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D5">
-        <v>-113</v>
+        <v>-132</v>
       </c>
       <c r="E5">
-        <v>-107</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5">
-        <v>824801</v>
+        <v>823664</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1133,46 +1130,46 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>0.1404</v>
+        <v>0.2638</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="P5">
-        <v>4.62</v>
+        <v>4.26</v>
       </c>
       <c r="Q5">
-        <v>0.1215</v>
+        <v>0.2458</v>
       </c>
       <c r="R5">
-        <v>0.349</v>
+        <v>0.371</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2613</v>
+        <v>0.2362</v>
       </c>
       <c r="U5">
-        <v>0.2658</v>
+        <v>0.2336</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2463</v>
+        <v>0.22</v>
       </c>
       <c r="X5">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y5">
-        <v>1.0657</v>
+        <v>1.0473</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1181,22 +1178,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.64</v>
+        <v>6.91</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF5">
-        <v>0.1338</v>
+        <v>0.2571</v>
       </c>
       <c r="AG5">
-        <v>1.185</v>
+        <v>1.0708</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>3.64</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1204,76 +1201,67 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-      <c r="D6">
-        <v>120</v>
-      </c>
-      <c r="E6">
-        <v>-147</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>824801</v>
+        <v>824640</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="I6">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0.2263</v>
+        <v>0.2261</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="P6">
-        <v>4.38</v>
+        <v>4.04</v>
       </c>
       <c r="Q6">
-        <v>0.2136</v>
+        <v>0.2857</v>
       </c>
       <c r="R6">
-        <v>0.34</v>
+        <v>0.095</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2335</v>
+        <v>0.2115</v>
       </c>
       <c r="U6">
-        <v>0.2465</v>
+        <v>0.2131</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2369</v>
+        <v>0.2179</v>
       </c>
       <c r="X6">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y6">
-        <v>1.0727</v>
+        <v>0.8952</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1282,22 +1270,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>5.64</v>
+        <v>1.7</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.222</v>
+        <v>0.2318</v>
       </c>
       <c r="AG6">
-        <v>1.059</v>
+        <v>0.9587</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>5.64</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1305,22 +1293,22 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E7">
-        <v>-134</v>
+        <v>-170</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>824476</v>
+        <v>824640</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
@@ -1335,46 +1323,46 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>0.2871</v>
+        <v>0.1799</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P7">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="Q7">
-        <v>0.292</v>
+        <v>0.1727</v>
       </c>
       <c r="R7">
-        <v>0.361</v>
+        <v>0.355</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2089</v>
+        <v>0.248</v>
       </c>
       <c r="U7">
-        <v>0.2069</v>
+        <v>0.2503</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2131</v>
+        <v>0.2352</v>
       </c>
       <c r="X7">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y7">
-        <v>0.8863</v>
+        <v>1.0504</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1383,22 +1371,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>5.55</v>
+        <v>4.85</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.2889</v>
+        <v>0.1773</v>
       </c>
       <c r="AG7">
-        <v>0.9472</v>
+        <v>1.1241</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>5.55</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1406,28 +1394,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="D8">
-        <v>-114</v>
+        <v>135</v>
       </c>
       <c r="E8">
-        <v>-104</v>
+        <v>-185</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G8">
-        <v>824476</v>
+        <v>824722</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1436,46 +1424,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>0.2235</v>
+        <v>0.1712</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="P8">
-        <v>4.36</v>
+        <v>4.1</v>
       </c>
       <c r="Q8">
-        <v>0.2617</v>
+        <v>0.1951</v>
       </c>
       <c r="R8">
-        <v>0.349</v>
+        <v>0.381</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2942</v>
+        <v>0.1864</v>
       </c>
       <c r="U8">
-        <v>0.2795</v>
+        <v>0.1979</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2505</v>
+        <v>0.2153</v>
       </c>
       <c r="X8">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y8">
-        <v>1.0673</v>
+        <v>1.0088</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1484,22 +1472,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>7.29</v>
+        <v>3.73</v>
       </c>
       <c r="AE8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2368</v>
+        <v>0.1803</v>
       </c>
       <c r="AG8">
-        <v>1.3341</v>
+        <v>0.8451</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>7.29</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1507,28 +1495,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C9">
         <v>5.5</v>
       </c>
       <c r="D9">
-        <v>115</v>
+        <v>-120</v>
       </c>
       <c r="E9">
-        <v>-137</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>822937</v>
+        <v>824722</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1537,46 +1525,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>0.2628</v>
+        <v>0.2774</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P9">
-        <v>3.91</v>
+        <v>4.03</v>
       </c>
       <c r="Q9">
-        <v>0.307</v>
+        <v>0.3276</v>
       </c>
       <c r="R9">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2319</v>
+        <v>0.2328</v>
       </c>
       <c r="U9">
-        <v>0.2142</v>
+        <v>0.1756</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.1898</v>
+        <v>0.1766</v>
       </c>
       <c r="X9">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y9">
-        <v>1.0855</v>
+        <v>0.88</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1585,22 +1573,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>7</v>
+        <v>6.32</v>
       </c>
       <c r="AE9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AF9">
-        <v>0.2789</v>
+        <v>0.2958</v>
       </c>
       <c r="AG9">
-        <v>1.0516</v>
+        <v>1.0553</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>7</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1608,28 +1596,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D10">
-        <v>-110</v>
+        <v>124</v>
       </c>
       <c r="E10">
-        <v>-109</v>
+        <v>-145</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G10">
-        <v>822937</v>
+        <v>823424</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1638,46 +1626,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>0.1713</v>
+        <v>0.1809</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="P10">
-        <v>4.41</v>
+        <v>4.12</v>
       </c>
       <c r="Q10">
-        <v>0.2165</v>
+        <v>0.1667</v>
       </c>
       <c r="R10">
-        <v>0.327</v>
+        <v>0.387</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.1894</v>
+        <v>0.1831</v>
       </c>
       <c r="U10">
-        <v>0.1807</v>
+        <v>0.1751</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.1884</v>
+        <v>0.2232</v>
       </c>
       <c r="X10">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y10">
-        <v>0.88</v>
+        <v>0.9247</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1686,22 +1674,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>2.55</v>
+        <v>3.61</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.186</v>
+        <v>0.1754</v>
       </c>
       <c r="AG10">
-        <v>0.8592</v>
+        <v>0.8299</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>2.55</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1709,28 +1697,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D11">
-        <v>110</v>
+        <v>-124</v>
       </c>
       <c r="E11">
-        <v>-124</v>
+        <v>108</v>
       </c>
       <c r="F11" t="s">
         <v>61</v>
       </c>
       <c r="G11">
-        <v>824394</v>
+        <v>823424</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1739,46 +1727,46 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>0.2513</v>
+        <v>0.2445</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="P11">
-        <v>3.97</v>
+        <v>4.34</v>
       </c>
       <c r="Q11">
-        <v>0.2667</v>
+        <v>0.2768</v>
       </c>
       <c r="R11">
-        <v>0.375</v>
+        <v>0.359</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2335</v>
+        <v>0.2385</v>
       </c>
       <c r="U11">
-        <v>0.2204</v>
+        <v>0.2228</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2287</v>
+        <v>0.2119</v>
       </c>
       <c r="X11">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y11">
-        <v>1.0313</v>
+        <v>0.9512</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1787,22 +1775,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>6.61</v>
+        <v>5.97</v>
       </c>
       <c r="AE11" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.2571</v>
+        <v>0.2561</v>
       </c>
       <c r="AG11">
-        <v>1.0589</v>
+        <v>1.081</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>6.61</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1813,25 +1801,25 @@
         <v>63</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D12">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E12">
-        <v>-137</v>
+        <v>-147</v>
       </c>
       <c r="F12" t="s">
         <v>64</v>
       </c>
       <c r="G12">
-        <v>823748</v>
+        <v>824801</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1843,43 +1831,43 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.2662</v>
+        <v>0.2296</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="P12">
-        <v>3.93</v>
+        <v>4.38</v>
       </c>
       <c r="Q12">
-        <v>0.2705</v>
+        <v>0.2581</v>
       </c>
       <c r="R12">
-        <v>0.379</v>
+        <v>0.317</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2211</v>
+        <v>0.2335</v>
       </c>
       <c r="U12">
-        <v>0.2203</v>
+        <v>0.2465</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2141</v>
+        <v>0.2369</v>
       </c>
       <c r="X12">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y12">
-        <v>0.975</v>
+        <v>1.0727</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1888,22 +1876,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>6.23</v>
+        <v>5.9</v>
       </c>
       <c r="AE12" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.2678</v>
+        <v>0.2386</v>
       </c>
       <c r="AG12">
-        <v>1.0028</v>
+        <v>1.0585</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>6.23</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1914,25 +1902,25 @@
         <v>65</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D13">
-        <v>110</v>
+        <v>-113</v>
       </c>
       <c r="E13">
-        <v>-135</v>
+        <v>-107</v>
       </c>
       <c r="F13" t="s">
         <v>64</v>
       </c>
       <c r="G13">
-        <v>823748</v>
+        <v>824801</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1944,43 +1932,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2308</v>
+        <v>0.1367</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="P13">
-        <v>4.16</v>
+        <v>4.64</v>
       </c>
       <c r="Q13">
-        <v>0.2373</v>
+        <v>0.1089</v>
       </c>
       <c r="R13">
-        <v>0.371</v>
+        <v>0.336</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2105</v>
+        <v>0.2613</v>
       </c>
       <c r="U13">
-        <v>0.1973</v>
+        <v>0.2658</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2245</v>
+        <v>0.2463</v>
       </c>
       <c r="X13">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y13">
-        <v>0.9742</v>
+        <v>1.0657</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1989,22 +1977,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.78</v>
+        <v>3.38</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2332</v>
+        <v>0.1274</v>
       </c>
       <c r="AG13">
-        <v>0.9549</v>
+        <v>1.1845</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.78</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2015,25 +2003,25 @@
         <v>66</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D14">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="E14">
-        <v>-150</v>
+        <v>-124</v>
       </c>
       <c r="F14" t="s">
         <v>67</v>
       </c>
       <c r="G14">
-        <v>824076</v>
+        <v>824394</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2045,43 +2033,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1821</v>
+        <v>0.253</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="P14">
-        <v>4.26</v>
+        <v>3.97</v>
       </c>
       <c r="Q14">
-        <v>0.1583</v>
+        <v>0.2719</v>
       </c>
       <c r="R14">
-        <v>0.375</v>
+        <v>0.363</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2016</v>
+        <v>0.2335</v>
       </c>
       <c r="U14">
-        <v>0.1918</v>
+        <v>0.2204</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2132</v>
+        <v>0.2287</v>
       </c>
       <c r="X14">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y14">
-        <v>1.0355</v>
+        <v>1.0313</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2090,22 +2078,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.89</v>
+        <v>6.59</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF14">
-        <v>0.1732</v>
+        <v>0.2599</v>
       </c>
       <c r="AG14">
-        <v>0.9143</v>
+        <v>1.0584</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>3.89</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2116,19 +2104,19 @@
         <v>68</v>
       </c>
       <c r="C15">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D15">
-        <v>118</v>
+        <v>-114</v>
       </c>
       <c r="E15">
-        <v>-147</v>
+        <v>-104</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G15">
-        <v>824076</v>
+        <v>824476</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
@@ -2143,46 +2131,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1837</v>
+        <v>0.225</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="P15">
-        <v>4.44</v>
+        <v>4.34</v>
       </c>
       <c r="Q15">
-        <v>0.1</v>
+        <v>0.2609</v>
       </c>
       <c r="R15">
-        <v>0.333</v>
+        <v>0.315</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2</v>
+        <v>0.2942</v>
       </c>
       <c r="U15">
-        <v>0.2033</v>
+        <v>0.2795</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2167</v>
+        <v>0.2505</v>
       </c>
       <c r="X15">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y15">
-        <v>0.9044</v>
+        <v>1.0673</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2191,22 +2179,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>2.79</v>
+        <v>7.12</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="AF15">
-        <v>0.1562</v>
+        <v>0.2363</v>
       </c>
       <c r="AG15">
-        <v>0.9072</v>
+        <v>1.3335</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>2.79</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2214,28 +2202,28 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+      <c r="D16">
+        <v>112</v>
+      </c>
+      <c r="E16">
+        <v>-134</v>
+      </c>
+      <c r="F16" t="s">
         <v>69</v>
       </c>
-      <c r="C16">
-        <v>4.5</v>
-      </c>
-      <c r="D16">
-        <v>110</v>
-      </c>
-      <c r="E16">
-        <v>-118</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
-      </c>
       <c r="G16">
-        <v>822860</v>
+        <v>824476</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2247,43 +2235,43 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>0.2095</v>
+        <v>0.2894</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="P16">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="Q16">
-        <v>0.2241</v>
+        <v>0.2981</v>
       </c>
       <c r="R16">
-        <v>0.367</v>
+        <v>0.342</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2033</v>
+        <v>0.2089</v>
       </c>
       <c r="U16">
-        <v>0.2026</v>
+        <v>0.2069</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2078</v>
+        <v>0.2131</v>
       </c>
       <c r="X16">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y16">
-        <v>0.9473</v>
+        <v>0.8863</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2292,22 +2280,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.03</v>
+        <v>5.51</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.2149</v>
+        <v>0.2924</v>
       </c>
       <c r="AG16">
-        <v>0.9219</v>
+        <v>0.9468</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>4.03</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2315,28 +2303,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D17">
-        <v>-140</v>
+        <v>-110</v>
       </c>
       <c r="E17">
-        <v>125</v>
+        <v>-109</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G17">
-        <v>822860</v>
+        <v>822937</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I17">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2348,43 +2336,43 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2612</v>
+        <v>0.1606</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="P17">
-        <v>4.23</v>
+        <v>4.39</v>
       </c>
       <c r="Q17">
-        <v>0.2581</v>
+        <v>0.1868</v>
       </c>
       <c r="R17">
-        <v>0.383</v>
+        <v>0.313</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2527</v>
+        <v>0.1894</v>
       </c>
       <c r="U17">
-        <v>0.2393</v>
+        <v>0.1807</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.222</v>
+        <v>0.1884</v>
       </c>
       <c r="X17">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y17">
-        <v>1.0139</v>
+        <v>0.88</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2393,22 +2381,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>6.72</v>
+        <v>2.24</v>
       </c>
       <c r="AE17" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.26</v>
+        <v>0.1688</v>
       </c>
       <c r="AG17">
-        <v>1.1461</v>
+        <v>0.8588</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>6.72</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2416,34 +2404,76 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D18">
-        <v>-117</v>
+        <v>115</v>
       </c>
       <c r="E18">
-        <v>105</v>
+        <v>-137</v>
       </c>
       <c r="F18" t="s">
         <v>73</v>
       </c>
-      <c r="G18" t="s">
-        <v>44</v>
+      <c r="G18">
+        <v>822937</v>
       </c>
       <c r="H18" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I18">
+        <v>5.6</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
+      <c r="M18">
+        <v>0.2635</v>
+      </c>
+      <c r="N18">
+        <v>5</v>
+      </c>
+      <c r="O18">
+        <v>105</v>
+      </c>
+      <c r="P18">
+        <v>3.9</v>
+      </c>
+      <c r="Q18">
+        <v>0.3238</v>
+      </c>
+      <c r="R18">
+        <v>0.344</v>
+      </c>
       <c r="S18" t="s">
-        <v>44</v>
-      </c>
-      <c r="V18" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T18">
+        <v>0.2319</v>
+      </c>
+      <c r="U18">
+        <v>0.2142</v>
+      </c>
+      <c r="V18">
+        <v>9</v>
+      </c>
+      <c r="W18">
+        <v>0.1898</v>
+      </c>
+      <c r="X18">
+        <v>0.2206</v>
+      </c>
+      <c r="Y18">
+        <v>1.0855</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2451,8 +2481,23 @@
       <c r="AC18" t="s">
         <v>44</v>
       </c>
+      <c r="AD18">
+        <v>7.03</v>
+      </c>
       <c r="AE18" t="s">
-        <v>44</v>
+        <v>70</v>
+      </c>
+      <c r="AF18">
+        <v>0.2842</v>
+      </c>
+      <c r="AG18">
+        <v>1.0511</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>7.03</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2460,28 +2505,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D19">
-        <v>-150</v>
+        <v>118</v>
       </c>
       <c r="E19">
-        <v>126</v>
+        <v>-147</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19">
-        <v>824318</v>
+        <v>824076</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2490,34 +2535,34 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M19">
-        <v>0.2293</v>
+        <v>0.1837</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>4.24</v>
+        <v>4.44</v>
       </c>
       <c r="Q19">
-        <v>0.2353</v>
+        <v>0.1</v>
       </c>
       <c r="R19">
-        <v>0.373</v>
+        <v>0.333</v>
       </c>
       <c r="S19" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2228</v>
+        <v>0.2</v>
       </c>
       <c r="U19">
-        <v>0.2203</v>
+        <v>0.2033</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2526,10 +2571,10 @@
         <v>0.2167</v>
       </c>
       <c r="X19">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y19">
-        <v>1.0193</v>
+        <v>0.9044</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2538,22 +2583,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.35</v>
+        <v>2.79</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2315</v>
+        <v>0.1562</v>
       </c>
       <c r="AG19">
-        <v>1.0105</v>
+        <v>0.9068</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.35</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2564,25 +2609,25 @@
         <v>77</v>
       </c>
       <c r="C20">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D20">
-        <v>-136</v>
+        <v>130</v>
       </c>
       <c r="E20">
-        <v>122</v>
+        <v>-150</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20">
-        <v>824318</v>
+        <v>824076</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2594,43 +2639,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.1828</v>
+        <v>0.1821</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="P20">
-        <v>4.44</v>
+        <v>4.26</v>
       </c>
       <c r="Q20">
-        <v>0.1418</v>
+        <v>0.1583</v>
       </c>
       <c r="R20">
-        <v>0.401</v>
+        <v>0.375</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2076</v>
+        <v>0.2016</v>
       </c>
       <c r="U20">
-        <v>0.1836</v>
+        <v>0.1918</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2007</v>
+        <v>0.2132</v>
       </c>
       <c r="X20">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y20">
-        <v>0.9455</v>
+        <v>1.0355</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2639,22 +2684,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>3.61</v>
+        <v>3.89</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.1664</v>
+        <v>0.1732</v>
       </c>
       <c r="AG20">
-        <v>0.9417</v>
+        <v>0.9139</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>3.61</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2668,22 +2713,22 @@
         <v>6.5</v>
       </c>
       <c r="D21">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="E21">
-        <v>-162</v>
+        <v>-137</v>
       </c>
       <c r="F21" t="s">
         <v>79</v>
       </c>
       <c r="G21">
-        <v>823342</v>
+        <v>823748</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2692,46 +2737,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2984</v>
+        <v>0.2662</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="P21">
-        <v>4.12</v>
+        <v>3.93</v>
       </c>
       <c r="Q21">
-        <v>0.3056</v>
+        <v>0.2705</v>
       </c>
       <c r="R21">
-        <v>0.351</v>
+        <v>0.379</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.183</v>
+        <v>0.2211</v>
       </c>
       <c r="U21">
-        <v>0.1827</v>
+        <v>0.2203</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2231</v>
+        <v>0.2141</v>
       </c>
       <c r="X21">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y21">
-        <v>0.9157</v>
+        <v>0.975</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2740,22 +2785,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.04</v>
+        <v>6.23</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF21">
-        <v>0.3009</v>
+        <v>0.2678</v>
       </c>
       <c r="AG21">
-        <v>0.8297</v>
+        <v>1.0023</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.04</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2766,25 +2811,25 @@
         <v>80</v>
       </c>
       <c r="C22">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D22">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E22">
-        <v>-165</v>
+        <v>-135</v>
       </c>
       <c r="F22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G22">
-        <v>823587</v>
+        <v>823748</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2793,34 +2838,34 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2098</v>
+        <v>0.2308</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P22">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
       <c r="Q22">
-        <v>0.2101</v>
+        <v>0.2373</v>
       </c>
       <c r="R22">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
       </c>
       <c r="T22">
-        <v>0.236</v>
+        <v>0.2105</v>
       </c>
       <c r="U22">
-        <v>0.2368</v>
+        <v>0.1973</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2829,10 +2874,10 @@
         <v>0.2245</v>
       </c>
       <c r="X22">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y22">
-        <v>0.9921</v>
+        <v>0.9742</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2841,22 +2886,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.23</v>
+        <v>4.78</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2099</v>
+        <v>0.2332</v>
       </c>
       <c r="AG22">
-        <v>1.0702</v>
+        <v>0.9545</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.23</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2864,28 +2909,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23">
+        <v>5.5</v>
+      </c>
+      <c r="D23">
+        <v>-140</v>
+      </c>
+      <c r="E23">
+        <v>125</v>
+      </c>
+      <c r="F23" t="s">
         <v>82</v>
       </c>
-      <c r="C23">
-        <v>3.5</v>
-      </c>
-      <c r="D23">
-        <v>-139</v>
-      </c>
-      <c r="E23">
-        <v>120</v>
-      </c>
-      <c r="F23" t="s">
-        <v>81</v>
-      </c>
       <c r="G23">
-        <v>823587</v>
+        <v>822860</v>
       </c>
       <c r="H23" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="I23">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2897,43 +2942,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2346</v>
+        <v>0.2612</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="P23">
-        <v>4.8</v>
+        <v>4.23</v>
       </c>
       <c r="Q23">
-        <v>0.2346</v>
+        <v>0.2581</v>
       </c>
       <c r="R23">
-        <v>0.288</v>
+        <v>0.383</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
       </c>
       <c r="T23">
-        <v>0.187</v>
+        <v>0.2527</v>
       </c>
       <c r="U23">
-        <v>0.1827</v>
+        <v>0.2393</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.217</v>
+        <v>0.222</v>
       </c>
       <c r="X23">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y23">
-        <v>1.0272</v>
+        <v>1.0139</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2942,22 +2987,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.09</v>
+        <v>6.71</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AF23">
-        <v>0.2346</v>
+        <v>0.26</v>
       </c>
       <c r="AG23">
-        <v>0.8483</v>
+        <v>1.1456</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.09</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2968,25 +3013,25 @@
         <v>83</v>
       </c>
       <c r="C24">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24">
-        <v>-132</v>
+        <v>110</v>
       </c>
       <c r="E24">
-        <v>108</v>
+        <v>-118</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G24">
-        <v>823664</v>
+        <v>822860</v>
       </c>
       <c r="H24" t="s">
         <v>42</v>
       </c>
       <c r="I24">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2995,46 +3040,46 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>0.2638</v>
+        <v>0.2095</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P24">
-        <v>4.26</v>
+        <v>4.36</v>
       </c>
       <c r="Q24">
-        <v>0.2458</v>
+        <v>0.2241</v>
       </c>
       <c r="R24">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="S24" t="s">
         <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2362</v>
+        <v>0.2033</v>
       </c>
       <c r="U24">
-        <v>0.2336</v>
+        <v>0.2026</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.22</v>
+        <v>0.2078</v>
       </c>
       <c r="X24">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y24">
-        <v>1.0473</v>
+        <v>0.9473</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3043,22 +3088,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>6.91</v>
+        <v>4.03</v>
       </c>
       <c r="AE24" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.2571</v>
+        <v>0.2149</v>
       </c>
       <c r="AG24">
-        <v>1.0713</v>
+        <v>0.9215</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>6.91</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3066,22 +3111,22 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" t="s">
         <v>85</v>
       </c>
-      <c r="F25" t="s">
-        <v>86</v>
-      </c>
       <c r="G25">
-        <v>824640</v>
+        <v>824155</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="I25">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3090,43 +3135,43 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0.2261</v>
+        <v>0.2222</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="P25">
-        <v>4.04</v>
+        <v>4.26</v>
       </c>
       <c r="Q25">
-        <v>0.2857</v>
+        <v>0.2286</v>
       </c>
       <c r="R25">
-        <v>0.095</v>
+        <v>0.344</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2115</v>
+        <v>0.2139</v>
       </c>
       <c r="U25">
-        <v>0.2131</v>
+        <v>0.2061</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2179</v>
+        <v>0.2173</v>
       </c>
       <c r="X25">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y25">
-        <v>0.8952</v>
+        <v>0.9671</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3135,22 +3180,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.2318</v>
+        <v>0.2244</v>
       </c>
       <c r="AG25">
-        <v>0.9591</v>
+        <v>0.9695</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3158,28 +3203,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C26">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26">
-        <v>125</v>
+        <v>-150</v>
       </c>
       <c r="E26">
-        <v>-170</v>
+        <v>126</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G26">
-        <v>824640</v>
+        <v>824318</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3188,46 +3233,46 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1799</v>
+        <v>0.2293</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="P26">
-        <v>4.05</v>
+        <v>4.24</v>
       </c>
       <c r="Q26">
-        <v>0.1727</v>
+        <v>0.2353</v>
       </c>
       <c r="R26">
-        <v>0.355</v>
+        <v>0.373</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.248</v>
+        <v>0.2258</v>
       </c>
       <c r="U26">
-        <v>0.2503</v>
+        <v>0.2024</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2352</v>
+        <v>0.2167</v>
       </c>
       <c r="X26">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y26">
-        <v>1.0504</v>
+        <v>1.0079</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3236,22 +3281,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.85</v>
+        <v>5.36</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.1773</v>
+        <v>0.2315</v>
       </c>
       <c r="AG26">
-        <v>1.1246</v>
+        <v>1.0238</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.85</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3259,28 +3304,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D27">
-        <v>-120</v>
+        <v>-136</v>
       </c>
       <c r="E27">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="G27">
-        <v>824722</v>
+        <v>824318</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3289,46 +3334,46 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>0.2774</v>
+        <v>0.1828</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="P27">
-        <v>4.03</v>
+        <v>4.44</v>
       </c>
       <c r="Q27">
-        <v>0.3276</v>
+        <v>0.1418</v>
       </c>
       <c r="R27">
-        <v>0.367</v>
+        <v>0.401</v>
       </c>
       <c r="S27" t="s">
         <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2328</v>
+        <v>0.2076</v>
       </c>
       <c r="U27">
-        <v>0.1756</v>
+        <v>0.1836</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.1747</v>
+        <v>0.2007</v>
       </c>
       <c r="X27">
-        <v>0.2205</v>
+        <v>0.2206</v>
       </c>
       <c r="Y27">
-        <v>0.88</v>
+        <v>0.9455</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3337,22 +3382,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>6.32</v>
+        <v>3.61</v>
       </c>
       <c r="AE27" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.2958</v>
+        <v>0.1664</v>
       </c>
       <c r="AG27">
-        <v>1.0558</v>
+        <v>0.9413</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>6.32</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3360,67 +3405,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="C28">
+        <v>4.5</v>
+      </c>
+      <c r="D28">
+        <v>-117</v>
+      </c>
+      <c r="E28">
+        <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>73</v>
-      </c>
-      <c r="G28">
-        <v>824155</v>
+        <v>85</v>
+      </c>
+      <c r="G28" t="s">
+        <v>44</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
-      </c>
-      <c r="I28">
-        <v>5.3</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0.2222</v>
-      </c>
-      <c r="N28">
-        <v>5</v>
-      </c>
-      <c r="O28">
-        <v>105</v>
-      </c>
-      <c r="P28">
-        <v>4.26</v>
-      </c>
-      <c r="Q28">
-        <v>0.2286</v>
-      </c>
-      <c r="R28">
-        <v>0.344</v>
+        <v>6</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
-      </c>
-      <c r="T28">
-        <v>0.2139</v>
-      </c>
-      <c r="U28">
-        <v>0.2061</v>
-      </c>
-      <c r="V28">
-        <v>9</v>
-      </c>
-      <c r="W28">
-        <v>0.2173</v>
-      </c>
-      <c r="X28">
-        <v>0.2205</v>
-      </c>
-      <c r="Y28">
-        <v>0.9671</v>
+        <v>44</v>
+      </c>
+      <c r="V28" t="s">
+        <v>44</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3428,23 +3440,8 @@
       <c r="AC28" t="s">
         <v>44</v>
       </c>
-      <c r="AD28">
-        <v>4.76</v>
-      </c>
       <c r="AE28" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF28">
-        <v>0.2244</v>
-      </c>
-      <c r="AG28">
-        <v>0.97</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>4.76</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3452,7 +3449,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C29">
         <v>3.5</v>
@@ -3464,7 +3461,7 @@
         <v>180</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G29" t="s">
         <v>44</v>
@@ -3496,7 +3493,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30">
         <v>4.5</v>
@@ -3508,7 +3505,7 @@
         <v>-117</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="G30" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-19.xlsx
+++ b/data/k-props/2026-08-19.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="96">
   <si>
     <t>date</t>
   </si>
@@ -145,22 +145,34 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Michael King</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ New York Mets</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Robert Stock</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Michael King</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ New York Mets</t>
-  </si>
-  <si>
-    <t>Robert Stock</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
   </si>
   <si>
     <t>Taj Bradley</t>
@@ -868,17 +880,23 @@
       <c r="Y2">
         <v>0.9157</v>
       </c>
+      <c r="Z2">
+        <v>5</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>-1.46</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>5.04</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.3009</v>
@@ -888,6 +906,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ2">
+        <v>0.04</v>
+      </c>
+      <c r="AK2">
+        <v>-0.04</v>
+      </c>
+      <c r="AL2">
+        <v>0.04</v>
       </c>
       <c r="AM2">
         <v>5.04</v>
@@ -898,7 +928,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>4.5</v>
@@ -910,7 +940,7 @@
         <v>-165</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>823587</v>
@@ -969,17 +999,23 @@
       <c r="Y3">
         <v>0.9921</v>
       </c>
+      <c r="Z3">
+        <v>4</v>
+      </c>
       <c r="AA3" t="s">
         <v>44</v>
       </c>
+      <c r="AB3">
+        <v>0.73</v>
+      </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD3">
         <v>5.23</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.2099</v>
@@ -989,6 +1025,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>-1.23</v>
+      </c>
+      <c r="AJ3">
+        <v>1.23</v>
+      </c>
+      <c r="AK3">
+        <v>-1.23</v>
+      </c>
+      <c r="AL3">
+        <v>1.23</v>
       </c>
       <c r="AM3">
         <v>5.23</v>
@@ -999,7 +1047,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -1011,13 +1059,13 @@
         <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>823587</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I4">
         <v>4.2</v>
@@ -1070,17 +1118,23 @@
       <c r="Y4">
         <v>1.0272</v>
       </c>
+      <c r="Z4">
+        <v>6</v>
+      </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB4">
+        <v>0.59</v>
       </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD4">
         <v>4.09</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>0.2346</v>
@@ -1090,6 +1144,18 @@
       </c>
       <c r="AH4">
         <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>1.91</v>
+      </c>
+      <c r="AJ4">
+        <v>1.91</v>
+      </c>
+      <c r="AK4">
+        <v>1.91</v>
+      </c>
+      <c r="AL4">
+        <v>1.91</v>
       </c>
       <c r="AM4">
         <v>4.09</v>
@@ -1100,7 +1166,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>5.5</v>
@@ -1112,7 +1178,7 @@
         <v>108</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>823664</v>
@@ -1171,17 +1237,23 @@
       <c r="Y5">
         <v>1.0473</v>
       </c>
+      <c r="Z5">
+        <v>7</v>
+      </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB5">
+        <v>1.41</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD5">
         <v>6.91</v>
       </c>
       <c r="AE5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AF5">
         <v>0.2571</v>
@@ -1191,6 +1263,18 @@
       </c>
       <c r="AH5">
         <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0.09</v>
+      </c>
+      <c r="AJ5">
+        <v>0.09</v>
+      </c>
+      <c r="AK5">
+        <v>0.09</v>
+      </c>
+      <c r="AL5">
+        <v>0.09</v>
       </c>
       <c r="AM5">
         <v>6.91</v>
@@ -1201,16 +1285,16 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>824640</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I6">
         <v>2.1</v>
@@ -1264,16 +1348,16 @@
         <v>0.8952</v>
       </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD6">
         <v>1.7</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF6">
         <v>0.2318</v>
@@ -1293,7 +1377,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>3.5</v>
@@ -1305,7 +1389,7 @@
         <v>-170</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>824640</v>
@@ -1364,17 +1448,23 @@
       <c r="Y7">
         <v>1.0504</v>
       </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
       <c r="AA7" t="s">
         <v>44</v>
       </c>
+      <c r="AB7">
+        <v>1.35</v>
+      </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD7">
         <v>4.85</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF7">
         <v>0.1773</v>
@@ -1384,6 +1474,18 @@
       </c>
       <c r="AH7">
         <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>-3.85</v>
+      </c>
+      <c r="AJ7">
+        <v>3.85</v>
+      </c>
+      <c r="AK7">
+        <v>-3.85</v>
+      </c>
+      <c r="AL7">
+        <v>3.85</v>
       </c>
       <c r="AM7">
         <v>4.85</v>
@@ -1394,7 +1496,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>8.5</v>
@@ -1406,7 +1508,7 @@
         <v>-185</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>824722</v>
@@ -1465,17 +1567,23 @@
       <c r="Y8">
         <v>1.0088</v>
       </c>
+      <c r="Z8">
+        <v>8</v>
+      </c>
       <c r="AA8" t="s">
         <v>44</v>
       </c>
+      <c r="AB8">
+        <v>-4.77</v>
+      </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD8">
         <v>3.73</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.1803</v>
@@ -1485,6 +1593,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>4.27</v>
+      </c>
+      <c r="AJ8">
+        <v>4.27</v>
+      </c>
+      <c r="AK8">
+        <v>4.27</v>
+      </c>
+      <c r="AL8">
+        <v>4.27</v>
       </c>
       <c r="AM8">
         <v>3.73</v>
@@ -1495,7 +1615,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C9">
         <v>5.5</v>
@@ -1507,7 +1627,7 @@
         <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>824722</v>
@@ -1566,17 +1686,23 @@
       <c r="Y9">
         <v>0.88</v>
       </c>
+      <c r="Z9">
+        <v>6</v>
+      </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB9">
+        <v>0.82</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD9">
         <v>6.32</v>
       </c>
       <c r="AE9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AF9">
         <v>0.2958</v>
@@ -1586,6 +1712,18 @@
       </c>
       <c r="AH9">
         <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>-0.32</v>
+      </c>
+      <c r="AJ9">
+        <v>0.32</v>
+      </c>
+      <c r="AK9">
+        <v>-0.32</v>
+      </c>
+      <c r="AL9">
+        <v>0.32</v>
       </c>
       <c r="AM9">
         <v>6.32</v>
@@ -1596,7 +1734,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10">
         <v>4.5</v>
@@ -1608,7 +1746,7 @@
         <v>-145</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>823424</v>
@@ -1667,17 +1805,23 @@
       <c r="Y10">
         <v>0.9247</v>
       </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
       <c r="AA10" t="s">
         <v>44</v>
       </c>
+      <c r="AB10">
+        <v>-0.89</v>
+      </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD10">
         <v>3.61</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.1754</v>
@@ -1687,6 +1831,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>-2.61</v>
+      </c>
+      <c r="AJ10">
+        <v>2.61</v>
+      </c>
+      <c r="AK10">
+        <v>-2.61</v>
+      </c>
+      <c r="AL10">
+        <v>2.61</v>
       </c>
       <c r="AM10">
         <v>3.61</v>
@@ -1697,7 +1853,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C11">
         <v>5.5</v>
@@ -1709,7 +1865,7 @@
         <v>108</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>823424</v>
@@ -1768,17 +1924,23 @@
       <c r="Y11">
         <v>0.9512</v>
       </c>
+      <c r="Z11">
+        <v>8</v>
+      </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB11">
+        <v>0.47</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD11">
         <v>5.97</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.2561</v>
@@ -1788,6 +1950,18 @@
       </c>
       <c r="AH11">
         <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>2.03</v>
+      </c>
+      <c r="AJ11">
+        <v>2.03</v>
+      </c>
+      <c r="AK11">
+        <v>2.03</v>
+      </c>
+      <c r="AL11">
+        <v>2.03</v>
       </c>
       <c r="AM11">
         <v>5.97</v>
@@ -1798,7 +1972,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>5.5</v>
@@ -1810,7 +1984,7 @@
         <v>-147</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G12">
         <v>824801</v>
@@ -1869,17 +2043,23 @@
       <c r="Y12">
         <v>1.0727</v>
       </c>
+      <c r="Z12">
+        <v>5</v>
+      </c>
       <c r="AA12" t="s">
         <v>44</v>
       </c>
+      <c r="AB12">
+        <v>0.4</v>
+      </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD12">
         <v>5.9</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.2386</v>
@@ -1889,6 +2069,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>-0.9</v>
+      </c>
+      <c r="AJ12">
+        <v>0.9</v>
+      </c>
+      <c r="AK12">
+        <v>-0.9</v>
+      </c>
+      <c r="AL12">
+        <v>0.9</v>
       </c>
       <c r="AM12">
         <v>5.9</v>
@@ -1899,7 +2091,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -1911,7 +2103,7 @@
         <v>-107</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>824801</v>
@@ -1970,17 +2162,23 @@
       <c r="Y13">
         <v>1.0657</v>
       </c>
+      <c r="Z13">
+        <v>6</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB13">
+        <v>-1.12</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD13">
         <v>3.38</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF13">
         <v>0.1274</v>
@@ -1990,6 +2188,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>2.62</v>
+      </c>
+      <c r="AJ13">
+        <v>2.62</v>
+      </c>
+      <c r="AK13">
+        <v>2.62</v>
+      </c>
+      <c r="AL13">
+        <v>2.62</v>
       </c>
       <c r="AM13">
         <v>3.38</v>
@@ -2000,7 +2210,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C14">
         <v>6.5</v>
@@ -2012,7 +2222,7 @@
         <v>-124</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G14">
         <v>824394</v>
@@ -2071,17 +2281,23 @@
       <c r="Y14">
         <v>1.0313</v>
       </c>
+      <c r="Z14">
+        <v>10</v>
+      </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB14">
+        <v>0.09</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD14">
         <v>6.59</v>
       </c>
       <c r="AE14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AF14">
         <v>0.2599</v>
@@ -2091,6 +2307,18 @@
       </c>
       <c r="AH14">
         <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>3.41</v>
+      </c>
+      <c r="AJ14">
+        <v>3.41</v>
+      </c>
+      <c r="AK14">
+        <v>3.41</v>
+      </c>
+      <c r="AL14">
+        <v>3.41</v>
       </c>
       <c r="AM14">
         <v>6.59</v>
@@ -2101,7 +2329,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2113,7 +2341,7 @@
         <v>-104</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G15">
         <v>824476</v>
@@ -2172,17 +2400,23 @@
       <c r="Y15">
         <v>1.0673</v>
       </c>
+      <c r="Z15">
+        <v>9</v>
+      </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB15">
+        <v>1.62</v>
       </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD15">
         <v>7.12</v>
       </c>
       <c r="AE15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AF15">
         <v>0.2363</v>
@@ -2192,6 +2426,18 @@
       </c>
       <c r="AH15">
         <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>1.88</v>
+      </c>
+      <c r="AJ15">
+        <v>1.88</v>
+      </c>
+      <c r="AK15">
+        <v>1.88</v>
+      </c>
+      <c r="AL15">
+        <v>1.88</v>
       </c>
       <c r="AM15">
         <v>7.12</v>
@@ -2202,7 +2448,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C16">
         <v>6.5</v>
@@ -2214,7 +2460,7 @@
         <v>-134</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G16">
         <v>824476</v>
@@ -2273,17 +2519,23 @@
       <c r="Y16">
         <v>0.8863</v>
       </c>
+      <c r="Z16">
+        <v>8</v>
+      </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB16">
+        <v>-0.99</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD16">
         <v>5.51</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.2924</v>
@@ -2293,6 +2545,18 @@
       </c>
       <c r="AH16">
         <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>2.49</v>
+      </c>
+      <c r="AJ16">
+        <v>2.49</v>
+      </c>
+      <c r="AK16">
+        <v>2.49</v>
+      </c>
+      <c r="AL16">
+        <v>2.49</v>
       </c>
       <c r="AM16">
         <v>5.51</v>
@@ -2303,7 +2567,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C17">
         <v>3.5</v>
@@ -2315,13 +2579,13 @@
         <v>-109</v>
       </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G17">
         <v>822937</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I17">
         <v>4</v>
@@ -2374,17 +2638,23 @@
       <c r="Y17">
         <v>0.88</v>
       </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
       <c r="AA17" t="s">
         <v>44</v>
       </c>
+      <c r="AB17">
+        <v>-1.26</v>
+      </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD17">
         <v>2.24</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.1688</v>
@@ -2394,6 +2664,18 @@
       </c>
       <c r="AH17">
         <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>-1.24</v>
+      </c>
+      <c r="AJ17">
+        <v>1.24</v>
+      </c>
+      <c r="AK17">
+        <v>-1.24</v>
+      </c>
+      <c r="AL17">
+        <v>1.24</v>
       </c>
       <c r="AM17">
         <v>2.24</v>
@@ -2404,7 +2686,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C18">
         <v>5.5</v>
@@ -2416,7 +2698,7 @@
         <v>-137</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G18">
         <v>822937</v>
@@ -2475,17 +2757,23 @@
       <c r="Y18">
         <v>1.0855</v>
       </c>
+      <c r="Z18">
+        <v>5</v>
+      </c>
       <c r="AA18" t="s">
         <v>44</v>
       </c>
+      <c r="AB18">
+        <v>1.53</v>
+      </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD18">
         <v>7.03</v>
       </c>
       <c r="AE18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AF18">
         <v>0.2842</v>
@@ -2495,6 +2783,18 @@
       </c>
       <c r="AH18">
         <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>-2.03</v>
+      </c>
+      <c r="AJ18">
+        <v>2.03</v>
+      </c>
+      <c r="AK18">
+        <v>-2.03</v>
+      </c>
+      <c r="AL18">
+        <v>2.03</v>
       </c>
       <c r="AM18">
         <v>7.03</v>
@@ -2505,7 +2805,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C19">
         <v>3.5</v>
@@ -2517,7 +2817,7 @@
         <v>-147</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G19">
         <v>824076</v>
@@ -2576,17 +2876,23 @@
       <c r="Y19">
         <v>0.9044</v>
       </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
       <c r="AA19" t="s">
         <v>44</v>
       </c>
+      <c r="AB19">
+        <v>-0.71</v>
+      </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD19">
         <v>2.79</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.1562</v>
@@ -2596,6 +2902,18 @@
       </c>
       <c r="AH19">
         <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>-1.79</v>
+      </c>
+      <c r="AJ19">
+        <v>1.79</v>
+      </c>
+      <c r="AK19">
+        <v>-1.79</v>
+      </c>
+      <c r="AL19">
+        <v>1.79</v>
       </c>
       <c r="AM19">
         <v>2.79</v>
@@ -2606,7 +2924,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C20">
         <v>4.5</v>
@@ -2618,7 +2936,7 @@
         <v>-150</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>824076</v>
@@ -2677,17 +2995,23 @@
       <c r="Y20">
         <v>1.0355</v>
       </c>
+      <c r="Z20">
+        <v>3</v>
+      </c>
       <c r="AA20" t="s">
         <v>44</v>
       </c>
+      <c r="AB20">
+        <v>-0.61</v>
+      </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD20">
         <v>3.89</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>0.1732</v>
@@ -2697,6 +3021,18 @@
       </c>
       <c r="AH20">
         <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>-0.89</v>
+      </c>
+      <c r="AJ20">
+        <v>0.89</v>
+      </c>
+      <c r="AK20">
+        <v>-0.89</v>
+      </c>
+      <c r="AL20">
+        <v>0.89</v>
       </c>
       <c r="AM20">
         <v>3.89</v>
@@ -2707,7 +3043,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C21">
         <v>6.5</v>
@@ -2719,7 +3055,7 @@
         <v>-137</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G21">
         <v>823748</v>
@@ -2778,17 +3114,23 @@
       <c r="Y21">
         <v>0.975</v>
       </c>
+      <c r="Z21">
+        <v>5</v>
+      </c>
       <c r="AA21" t="s">
         <v>44</v>
       </c>
+      <c r="AB21">
+        <v>-0.27</v>
+      </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD21">
         <v>6.23</v>
       </c>
       <c r="AE21" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AF21">
         <v>0.2678</v>
@@ -2798,6 +3140,18 @@
       </c>
       <c r="AH21">
         <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>-1.23</v>
+      </c>
+      <c r="AJ21">
+        <v>1.23</v>
+      </c>
+      <c r="AK21">
+        <v>-1.23</v>
+      </c>
+      <c r="AL21">
+        <v>1.23</v>
       </c>
       <c r="AM21">
         <v>6.23</v>
@@ -2808,7 +3162,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2820,7 +3174,7 @@
         <v>-135</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G22">
         <v>823748</v>
@@ -2879,17 +3233,23 @@
       <c r="Y22">
         <v>0.9742</v>
       </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
       <c r="AA22" t="s">
         <v>44</v>
       </c>
+      <c r="AB22">
+        <v>-0.72</v>
+      </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD22">
         <v>4.78</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.2332</v>
@@ -2899,6 +3259,18 @@
       </c>
       <c r="AH22">
         <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>-3.78</v>
+      </c>
+      <c r="AJ22">
+        <v>3.78</v>
+      </c>
+      <c r="AK22">
+        <v>-3.78</v>
+      </c>
+      <c r="AL22">
+        <v>3.78</v>
       </c>
       <c r="AM22">
         <v>4.78</v>
@@ -2909,7 +3281,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C23">
         <v>5.5</v>
@@ -2921,7 +3293,7 @@
         <v>125</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G23">
         <v>822860</v>
@@ -2980,17 +3352,23 @@
       <c r="Y23">
         <v>1.0139</v>
       </c>
+      <c r="Z23">
+        <v>11</v>
+      </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB23">
+        <v>1.21</v>
       </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD23">
         <v>6.71</v>
       </c>
       <c r="AE23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AF23">
         <v>0.26</v>
@@ -3000,6 +3378,18 @@
       </c>
       <c r="AH23">
         <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>4.29</v>
+      </c>
+      <c r="AJ23">
+        <v>4.29</v>
+      </c>
+      <c r="AK23">
+        <v>4.29</v>
+      </c>
+      <c r="AL23">
+        <v>4.29</v>
       </c>
       <c r="AM23">
         <v>6.71</v>
@@ -3010,7 +3400,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C24">
         <v>4.5</v>
@@ -3022,7 +3412,7 @@
         <v>-118</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G24">
         <v>822860</v>
@@ -3081,17 +3471,23 @@
       <c r="Y24">
         <v>0.9473</v>
       </c>
+      <c r="Z24">
+        <v>3</v>
+      </c>
       <c r="AA24" t="s">
         <v>44</v>
       </c>
+      <c r="AB24">
+        <v>-0.47</v>
+      </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD24">
         <v>4.03</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF24">
         <v>0.2149</v>
@@ -3101,6 +3497,18 @@
       </c>
       <c r="AH24">
         <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>-1.03</v>
+      </c>
+      <c r="AJ24">
+        <v>1.03</v>
+      </c>
+      <c r="AK24">
+        <v>-1.03</v>
+      </c>
+      <c r="AL24">
+        <v>1.03</v>
       </c>
       <c r="AM24">
         <v>4.03</v>
@@ -3111,10 +3519,10 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G25">
         <v>824155</v>
@@ -3174,16 +3582,16 @@
         <v>0.9671</v>
       </c>
       <c r="AA25" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD25">
         <v>4.75</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF25">
         <v>0.2244</v>
@@ -3203,7 +3611,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -3215,7 +3623,7 @@
         <v>126</v>
       </c>
       <c r="F26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G26">
         <v>824318</v>
@@ -3274,17 +3682,23 @@
       <c r="Y26">
         <v>1.0079</v>
       </c>
+      <c r="Z26">
+        <v>6</v>
+      </c>
       <c r="AA26" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB26">
+        <v>0.86</v>
       </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD26">
         <v>5.36</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF26">
         <v>0.2315</v>
@@ -3294,6 +3708,18 @@
       </c>
       <c r="AH26">
         <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0.64</v>
+      </c>
+      <c r="AJ26">
+        <v>0.64</v>
+      </c>
+      <c r="AK26">
+        <v>0.64</v>
+      </c>
+      <c r="AL26">
+        <v>0.64</v>
       </c>
       <c r="AM26">
         <v>5.36</v>
@@ -3304,7 +3730,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3316,7 +3742,7 @@
         <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G27">
         <v>824318</v>
@@ -3375,17 +3801,23 @@
       <c r="Y27">
         <v>0.9455</v>
       </c>
+      <c r="Z27">
+        <v>5</v>
+      </c>
       <c r="AA27" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB27">
+        <v>0.11</v>
       </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD27">
         <v>3.61</v>
       </c>
       <c r="AE27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF27">
         <v>0.1664</v>
@@ -3395,6 +3827,18 @@
       </c>
       <c r="AH27">
         <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>1.39</v>
+      </c>
+      <c r="AJ27">
+        <v>1.39</v>
+      </c>
+      <c r="AK27">
+        <v>1.39</v>
+      </c>
+      <c r="AL27">
+        <v>1.39</v>
       </c>
       <c r="AM27">
         <v>3.61</v>
@@ -3405,7 +3849,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C28">
         <v>4.5</v>
@@ -3417,31 +3861,31 @@
         <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L28">
         <v>6</v>
       </c>
       <c r="S28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="V28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AA28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AE28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3449,7 +3893,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C29">
         <v>3.5</v>
@@ -3461,31 +3905,31 @@
         <v>180</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G29" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H29" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L29">
         <v>1</v>
       </c>
       <c r="S29" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="V29" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AA29" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AE29" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3493,7 +3937,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C30">
         <v>4.5</v>
@@ -3508,28 +3952,28 @@
         <v>41</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H30" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="S30" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="V30" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AE30" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
